--- a/astro-site/public/dl/kit-tareas-cafeteria/06-eventos-festivos.xlsx
+++ b/astro-site/public/dl/kit-tareas-cafeteria/06-eventos-festivos.xlsx
@@ -1,23 +1,23 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
-    <workbookView activeTab="0" autoFilterDateGrouping="1" firstSheet="0" minimized="0" showHorizontalScroll="1" showSheetTabs="1" showVerticalScroll="1" tabRatio="600" visibility="visible"/>
+    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Instrucciones" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="Brunch Dominical" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="San Valentín" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet name="Navidad" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet name="Temporada Terraza" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Instrucciones" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Brunch Dominical" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="San Valentín" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Navidad" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Temporada Terraza" sheetId="5" state="visible" r:id="rId5"/>
   </sheets>
   <definedNames>
-    <definedName localSheetId="1" name="_xlnm.Print_Area">'Brunch Dominical'!$A$1:$G$32</definedName>
-    <definedName localSheetId="2" name="_xlnm.Print_Area">'San Valentín'!$A$1:$G$22</definedName>
-    <definedName localSheetId="3" name="_xlnm.Print_Area">'Navidad'!$A$1:$G$29</definedName>
-    <definedName localSheetId="4" name="_xlnm.Print_Area">'Temporada Terraza'!$A$1:$G$24</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="1">'Brunch Dominical'!$A$1:$G$32</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="2">'San Valentín'!$A$1:$G$22</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="3">'Navidad'!$A$1:$G$29</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="4">'Temporada Terraza'!$A$1:$G$24</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -26,7 +26,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="11">
+  <fonts count="12">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -85,6 +85,11 @@
       <color rgb="00888888"/>
       <sz val="8"/>
     </font>
+    <font>
+      <name val="Calibri"/>
+      <color rgb="00666666"/>
+      <sz val="10"/>
+    </font>
   </fonts>
   <fills count="6">
     <fill>
@@ -142,50 +147,66 @@
     </border>
   </borders>
   <cellStyleXfs count="1">
-    <xf borderId="0" fillId="0" fontId="0" numFmtId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="20">
-    <xf borderId="0" fillId="0" fontId="0" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf borderId="0" fillId="0" fontId="1" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf borderId="0" fillId="0" fontId="2" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf borderId="0" fillId="0" fontId="3" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf applyAlignment="1" borderId="0" fillId="0" fontId="1" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0">
+  <cellXfs count="22">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf borderId="0" fillId="0" fontId="4" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf applyAlignment="1" borderId="1" fillId="2" fontId="5" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf applyAlignment="1" borderId="0" fillId="3" fontId="3" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf applyAlignment="1" borderId="1" fillId="4" fontId="6" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="6" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
     </xf>
-    <xf borderId="1" fillId="4" fontId="6" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf applyAlignment="1" borderId="1" fillId="4" fontId="7" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="6" fillId="4" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="7" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
     </xf>
-    <xf borderId="1" fillId="4" fontId="0" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf applyAlignment="1" borderId="1" fillId="5" fontId="6" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="6" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
     </xf>
-    <xf borderId="1" fillId="5" fontId="6" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf applyAlignment="1" borderId="1" fillId="5" fontId="7" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="6" fillId="5" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="7" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
     </xf>
-    <xf borderId="1" fillId="5" fontId="0" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf borderId="0" fillId="0" fontId="8" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf borderId="0" fillId="0" fontId="9" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf borderId="0" fillId="0" fontId="7" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf applyAlignment="1" borderId="0" fillId="0" fontId="10" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle builtinId="0" hidden="0" name="Normal" xfId="0"/>
+    <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
   </cellStyles>
-  <tableStyles count="0" defaultPivotStyle="PivotStyleLight16" defaultTableStyle="TableStyleMedium9"/>
+  <dxfs count="1">
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="00C8E6C9"/>
+          <bgColor rgb="00C8E6C9"/>
+        </patternFill>
+      </fill>
+    </dxf>
+  </dxfs>
+  <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
   <colors>
     <indexedColors>
       <rgbColor rgb="00000000"/>
@@ -545,15 +566,16 @@
   <sheetPr>
     <tabColor rgb="00FFD700"/>
     <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
+    <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="B2:B10"/>
+  <dimension ref="A1:B14"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col customWidth="1" max="1" min="1" width="4"/>
-    <col customWidth="1" max="2" min="2" width="80"/>
+    <col width="4" customWidth="1" min="1" max="1"/>
+    <col width="80" customWidth="1" min="2" max="2"/>
   </cols>
   <sheetData>
+    <row r="1"/>
     <row r="2">
       <c r="B2" s="1" t="inlineStr">
         <is>
@@ -561,6 +583,7 @@
         </is>
       </c>
     </row>
+    <row r="3"/>
     <row r="4">
       <c r="B4" s="2" t="inlineStr">
         <is>
@@ -568,6 +591,7 @@
         </is>
       </c>
     </row>
+    <row r="5"/>
     <row r="6">
       <c r="B6" s="2" t="inlineStr">
         <is>
@@ -589,6 +613,7 @@
         </is>
       </c>
     </row>
+    <row r="9"/>
     <row r="10">
       <c r="B10" s="3" t="inlineStr">
         <is>
@@ -596,8 +621,33 @@
         </is>
       </c>
     </row>
+    <row r="11"/>
+    <row r="12">
+      <c r="B12" s="3" t="inlineStr">
+        <is>
+          <t>Marca con ✓ en la columna «✓ Completada» (desplegable): es la que cuenta el total de tareas completadas.</t>
+        </is>
+      </c>
+    </row>
+    <row r="13"/>
+    <row r="14">
+      <c r="B14" s="3" t="inlineStr">
+        <is>
+          <t>Versión 1.1 · agosto 2026 · aichef.pro/kit-tareas-cafeteria · info@aichef.pro</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <pageMargins bottom="1" footer="0.5" header="0.5" left="0.75" right="0.75" top="1"/>
+  <pageMargins left="0.59" right="0.59" top="0.59" bottom="0.59" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" paperSize="9" fitToHeight="0" fitToWidth="1"/>
+  <headerFooter>
+    <oddHeader/>
+    <oddFooter>&amp;C&amp;8 AI Chef Pro · aichef.pro · Página &amp;P de &amp;N</oddFooter>
+    <evenHeader/>
+    <evenFooter/>
+    <firstHeader/>
+    <firstFooter/>
+  </headerFooter>
 </worksheet>
 </file>
 
@@ -611,16 +661,16 @@
   <dimension ref="A1:G32"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col customWidth="1" max="1" min="1" width="4"/>
-    <col customWidth="1" max="2" min="2" width="45"/>
-    <col customWidth="1" max="3" min="3" width="14"/>
-    <col customWidth="1" max="4" min="4" width="18"/>
-    <col customWidth="1" max="5" min="5" width="12"/>
-    <col customWidth="1" max="6" min="6" width="8"/>
-    <col customWidth="1" max="7" min="7" width="12"/>
+    <col width="4" customWidth="1" min="1" max="1"/>
+    <col width="45" customWidth="1" min="2" max="2"/>
+    <col width="14" customWidth="1" min="3" max="3"/>
+    <col width="18" customWidth="1" min="4" max="4"/>
+    <col width="12" customWidth="1" min="5" max="5"/>
+    <col width="8" customWidth="1" min="6" max="6"/>
+    <col width="12" customWidth="1" min="7" max="7"/>
   </cols>
   <sheetData>
-    <row customHeight="1" ht="30" r="1">
+    <row r="1" ht="30" customHeight="1">
       <c r="A1" s="4" t="inlineStr">
         <is>
           <t>Brunch Dominical Especial — Prep y Servicio</t>
@@ -634,10 +684,11 @@
         </is>
       </c>
     </row>
+    <row r="3"/>
     <row r="4">
       <c r="A4" s="6" t="inlineStr">
         <is>
-          <t>☐</t>
+          <t>Nº</t>
         </is>
       </c>
       <c r="B4" s="6" t="inlineStr">
@@ -662,7 +713,7 @@
       </c>
       <c r="F4" s="6" t="inlineStr">
         <is>
-          <t>Hecha</t>
+          <t>✓ Completada</t>
         </is>
       </c>
       <c r="G4" s="6" t="inlineStr">
@@ -679,10 +730,8 @@
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="8" t="inlineStr">
-        <is>
-          <t>☐</t>
-        </is>
+      <c r="A6" s="20" t="n">
+        <v>1</v>
       </c>
       <c r="B6" s="9" t="inlineStr">
         <is>
@@ -708,10 +757,8 @@
       <c r="G6" s="11" t="n"/>
     </row>
     <row r="7">
-      <c r="A7" s="12" t="inlineStr">
-        <is>
-          <t>☐</t>
-        </is>
+      <c r="A7" s="21" t="n">
+        <v>2</v>
       </c>
       <c r="B7" s="13" t="inlineStr">
         <is>
@@ -737,10 +784,8 @@
       <c r="G7" s="15" t="n"/>
     </row>
     <row r="8">
-      <c r="A8" s="8" t="inlineStr">
-        <is>
-          <t>☐</t>
-        </is>
+      <c r="A8" s="20" t="n">
+        <v>3</v>
       </c>
       <c r="B8" s="9" t="inlineStr">
         <is>
@@ -766,10 +811,8 @@
       <c r="G8" s="11" t="n"/>
     </row>
     <row r="9">
-      <c r="A9" s="12" t="inlineStr">
-        <is>
-          <t>☐</t>
-        </is>
+      <c r="A9" s="21" t="n">
+        <v>4</v>
       </c>
       <c r="B9" s="13" t="inlineStr">
         <is>
@@ -795,10 +838,8 @@
       <c r="G9" s="15" t="n"/>
     </row>
     <row r="10">
-      <c r="A10" s="8" t="inlineStr">
-        <is>
-          <t>☐</t>
-        </is>
+      <c r="A10" s="20" t="n">
+        <v>5</v>
       </c>
       <c r="B10" s="9" t="inlineStr">
         <is>
@@ -831,10 +872,8 @@
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="8" t="inlineStr">
-        <is>
-          <t>☐</t>
-        </is>
+      <c r="A12" s="20" t="n">
+        <v>6</v>
       </c>
       <c r="B12" s="9" t="inlineStr">
         <is>
@@ -860,10 +899,8 @@
       <c r="G12" s="11" t="n"/>
     </row>
     <row r="13">
-      <c r="A13" s="12" t="inlineStr">
-        <is>
-          <t>☐</t>
-        </is>
+      <c r="A13" s="21" t="n">
+        <v>7</v>
       </c>
       <c r="B13" s="13" t="inlineStr">
         <is>
@@ -889,10 +926,8 @@
       <c r="G13" s="15" t="n"/>
     </row>
     <row r="14">
-      <c r="A14" s="8" t="inlineStr">
-        <is>
-          <t>☐</t>
-        </is>
+      <c r="A14" s="20" t="n">
+        <v>8</v>
       </c>
       <c r="B14" s="9" t="inlineStr">
         <is>
@@ -918,10 +953,8 @@
       <c r="G14" s="11" t="n"/>
     </row>
     <row r="15">
-      <c r="A15" s="12" t="inlineStr">
-        <is>
-          <t>☐</t>
-        </is>
+      <c r="A15" s="21" t="n">
+        <v>9</v>
       </c>
       <c r="B15" s="13" t="inlineStr">
         <is>
@@ -947,10 +980,8 @@
       <c r="G15" s="15" t="n"/>
     </row>
     <row r="16">
-      <c r="A16" s="8" t="inlineStr">
-        <is>
-          <t>☐</t>
-        </is>
+      <c r="A16" s="20" t="n">
+        <v>10</v>
       </c>
       <c r="B16" s="9" t="inlineStr">
         <is>
@@ -983,10 +1014,8 @@
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="8" t="inlineStr">
-        <is>
-          <t>☐</t>
-        </is>
+      <c r="A18" s="20" t="n">
+        <v>11</v>
       </c>
       <c r="B18" s="9" t="inlineStr">
         <is>
@@ -1012,10 +1041,8 @@
       <c r="G18" s="11" t="n"/>
     </row>
     <row r="19">
-      <c r="A19" s="12" t="inlineStr">
-        <is>
-          <t>☐</t>
-        </is>
+      <c r="A19" s="21" t="n">
+        <v>12</v>
       </c>
       <c r="B19" s="13" t="inlineStr">
         <is>
@@ -1041,10 +1068,8 @@
       <c r="G19" s="15" t="n"/>
     </row>
     <row r="20">
-      <c r="A20" s="8" t="inlineStr">
-        <is>
-          <t>☐</t>
-        </is>
+      <c r="A20" s="20" t="n">
+        <v>13</v>
       </c>
       <c r="B20" s="9" t="inlineStr">
         <is>
@@ -1070,10 +1095,8 @@
       <c r="G20" s="11" t="n"/>
     </row>
     <row r="21">
-      <c r="A21" s="12" t="inlineStr">
-        <is>
-          <t>☐</t>
-        </is>
+      <c r="A21" s="21" t="n">
+        <v>14</v>
       </c>
       <c r="B21" s="13" t="inlineStr">
         <is>
@@ -1099,10 +1122,8 @@
       <c r="G21" s="15" t="n"/>
     </row>
     <row r="22">
-      <c r="A22" s="8" t="inlineStr">
-        <is>
-          <t>☐</t>
-        </is>
+      <c r="A22" s="20" t="n">
+        <v>15</v>
       </c>
       <c r="B22" s="9" t="inlineStr">
         <is>
@@ -1135,10 +1156,8 @@
       </c>
     </row>
     <row r="24">
-      <c r="A24" s="8" t="inlineStr">
-        <is>
-          <t>☐</t>
-        </is>
+      <c r="A24" s="20" t="n">
+        <v>16</v>
       </c>
       <c r="B24" s="9" t="inlineStr">
         <is>
@@ -1164,10 +1183,8 @@
       <c r="G24" s="11" t="n"/>
     </row>
     <row r="25">
-      <c r="A25" s="12" t="inlineStr">
-        <is>
-          <t>☐</t>
-        </is>
+      <c r="A25" s="21" t="n">
+        <v>17</v>
       </c>
       <c r="B25" s="13" t="inlineStr">
         <is>
@@ -1193,10 +1210,8 @@
       <c r="G25" s="15" t="n"/>
     </row>
     <row r="26">
-      <c r="A26" s="8" t="inlineStr">
-        <is>
-          <t>☐</t>
-        </is>
+      <c r="A26" s="20" t="n">
+        <v>18</v>
       </c>
       <c r="B26" s="9" t="inlineStr">
         <is>
@@ -1221,6 +1236,7 @@
       <c r="F26" s="11" t="n"/>
       <c r="G26" s="11" t="n"/>
     </row>
+    <row r="27"/>
     <row r="28">
       <c r="C28" s="16" t="inlineStr">
         <is>
@@ -1229,14 +1245,19 @@
       </c>
       <c r="D28" s="17">
         <f>COUNTIF(F5:F26,"✓")</f>
-        <v/>
+        <v>0.0</v>
       </c>
       <c r="E28" s="16" t="inlineStr">
         <is>
-          <t>de 18</t>
-        </is>
-      </c>
-    </row>
+          <t>de</t>
+        </is>
+      </c>
+      <c r="F28">
+        <f>COUNTIF(B5:B26,"?*")</f>
+        <v>18.0</v>
+      </c>
+    </row>
+    <row r="29"/>
     <row r="30">
       <c r="A30" s="18" t="inlineStr">
         <is>
@@ -1244,6 +1265,7 @@
         </is>
       </c>
     </row>
+    <row r="31"/>
     <row r="32">
       <c r="A32" s="19" t="inlineStr">
         <is>
@@ -1262,8 +1284,18 @@
     <mergeCell ref="A5:G5"/>
     <mergeCell ref="A11:G11"/>
   </mergeCells>
-  <pageMargins bottom="1" footer="0.5" header="0.5" left="0.75" right="0.75" top="1"/>
-  <pageSetup fitToHeight="0" fitToWidth="1" orientation="portrait" paperSize="9"/>
+  <conditionalFormatting sqref="A5:G26">
+    <cfRule type="expression" priority="1" dxfId="0">
+      <formula>$F5="✓"</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <dataValidations count="1">
+    <dataValidation sqref="F6 F7 F8 F9 F10 F12 F13 F14 F15 F16 F18 F19 F20 F21 F22 F24 F25 F26" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+      <formula1>"✓,—,N/A"</formula1>
+    </dataValidation>
+  </dataValidations>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <pageSetup orientation="portrait" paperSize="9" fitToHeight="0" fitToWidth="1"/>
 </worksheet>
 </file>
 
@@ -1277,16 +1309,16 @@
   <dimension ref="A1:G22"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col customWidth="1" max="1" min="1" width="4"/>
-    <col customWidth="1" max="2" min="2" width="45"/>
-    <col customWidth="1" max="3" min="3" width="14"/>
-    <col customWidth="1" max="4" min="4" width="18"/>
-    <col customWidth="1" max="5" min="5" width="12"/>
-    <col customWidth="1" max="6" min="6" width="8"/>
-    <col customWidth="1" max="7" min="7" width="12"/>
+    <col width="4" customWidth="1" min="1" max="1"/>
+    <col width="45" customWidth="1" min="2" max="2"/>
+    <col width="14" customWidth="1" min="3" max="3"/>
+    <col width="18" customWidth="1" min="4" max="4"/>
+    <col width="12" customWidth="1" min="5" max="5"/>
+    <col width="8" customWidth="1" min="6" max="6"/>
+    <col width="12" customWidth="1" min="7" max="7"/>
   </cols>
   <sheetData>
-    <row customHeight="1" ht="30" r="1">
+    <row r="1" ht="30" customHeight="1">
       <c r="A1" s="4" t="inlineStr">
         <is>
           <t>Tareas Específicas — San Valentín (14 de Febrero)</t>
@@ -1300,10 +1332,11 @@
         </is>
       </c>
     </row>
+    <row r="3"/>
     <row r="4">
       <c r="A4" s="6" t="inlineStr">
         <is>
-          <t>☐</t>
+          <t>Nº</t>
         </is>
       </c>
       <c r="B4" s="6" t="inlineStr">
@@ -1328,7 +1361,7 @@
       </c>
       <c r="F4" s="6" t="inlineStr">
         <is>
-          <t>Hecha</t>
+          <t>✓ Completada</t>
         </is>
       </c>
       <c r="G4" s="6" t="inlineStr">
@@ -1345,10 +1378,8 @@
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="8" t="inlineStr">
-        <is>
-          <t>☐</t>
-        </is>
+      <c r="A6" s="20" t="n">
+        <v>1</v>
       </c>
       <c r="B6" s="9" t="inlineStr">
         <is>
@@ -1374,10 +1405,8 @@
       <c r="G6" s="11" t="n"/>
     </row>
     <row r="7">
-      <c r="A7" s="12" t="inlineStr">
-        <is>
-          <t>☐</t>
-        </is>
+      <c r="A7" s="21" t="n">
+        <v>2</v>
       </c>
       <c r="B7" s="13" t="inlineStr">
         <is>
@@ -1403,10 +1432,8 @@
       <c r="G7" s="15" t="n"/>
     </row>
     <row r="8">
-      <c r="A8" s="8" t="inlineStr">
-        <is>
-          <t>☐</t>
-        </is>
+      <c r="A8" s="20" t="n">
+        <v>3</v>
       </c>
       <c r="B8" s="9" t="inlineStr">
         <is>
@@ -1432,10 +1459,8 @@
       <c r="G8" s="11" t="n"/>
     </row>
     <row r="9">
-      <c r="A9" s="12" t="inlineStr">
-        <is>
-          <t>☐</t>
-        </is>
+      <c r="A9" s="21" t="n">
+        <v>4</v>
       </c>
       <c r="B9" s="13" t="inlineStr">
         <is>
@@ -1468,10 +1493,8 @@
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="12" t="inlineStr">
-        <is>
-          <t>☐</t>
-        </is>
+      <c r="A11" s="21" t="n">
+        <v>5</v>
       </c>
       <c r="B11" s="13" t="inlineStr">
         <is>
@@ -1497,10 +1520,8 @@
       <c r="G11" s="15" t="n"/>
     </row>
     <row r="12">
-      <c r="A12" s="8" t="inlineStr">
-        <is>
-          <t>☐</t>
-        </is>
+      <c r="A12" s="20" t="n">
+        <v>6</v>
       </c>
       <c r="B12" s="9" t="inlineStr">
         <is>
@@ -1526,10 +1547,8 @@
       <c r="G12" s="11" t="n"/>
     </row>
     <row r="13">
-      <c r="A13" s="12" t="inlineStr">
-        <is>
-          <t>☐</t>
-        </is>
+      <c r="A13" s="21" t="n">
+        <v>7</v>
       </c>
       <c r="B13" s="13" t="inlineStr">
         <is>
@@ -1555,10 +1574,8 @@
       <c r="G13" s="15" t="n"/>
     </row>
     <row r="14">
-      <c r="A14" s="8" t="inlineStr">
-        <is>
-          <t>☐</t>
-        </is>
+      <c r="A14" s="20" t="n">
+        <v>8</v>
       </c>
       <c r="B14" s="9" t="inlineStr">
         <is>
@@ -1584,10 +1601,8 @@
       <c r="G14" s="11" t="n"/>
     </row>
     <row r="15">
-      <c r="A15" s="12" t="inlineStr">
-        <is>
-          <t>☐</t>
-        </is>
+      <c r="A15" s="21" t="n">
+        <v>9</v>
       </c>
       <c r="B15" s="13" t="inlineStr">
         <is>
@@ -1613,10 +1628,8 @@
       <c r="G15" s="15" t="n"/>
     </row>
     <row r="16">
-      <c r="A16" s="8" t="inlineStr">
-        <is>
-          <t>☐</t>
-        </is>
+      <c r="A16" s="20" t="n">
+        <v>10</v>
       </c>
       <c r="B16" s="9" t="inlineStr">
         <is>
@@ -1641,6 +1654,7 @@
       <c r="F16" s="11" t="n"/>
       <c r="G16" s="11" t="n"/>
     </row>
+    <row r="17"/>
     <row r="18">
       <c r="C18" s="16" t="inlineStr">
         <is>
@@ -1649,14 +1663,19 @@
       </c>
       <c r="D18" s="17">
         <f>COUNTIF(F5:F16,"✓")</f>
-        <v/>
+        <v>0.0</v>
       </c>
       <c r="E18" s="16" t="inlineStr">
         <is>
-          <t>de 10</t>
-        </is>
-      </c>
-    </row>
+          <t>de</t>
+        </is>
+      </c>
+      <c r="F18">
+        <f>COUNTIF(B5:B16,"?*")</f>
+        <v>10.0</v>
+      </c>
+    </row>
+    <row r="19"/>
     <row r="20">
       <c r="A20" s="18" t="inlineStr">
         <is>
@@ -1664,6 +1683,7 @@
         </is>
       </c>
     </row>
+    <row r="21"/>
     <row r="22">
       <c r="A22" s="19" t="inlineStr">
         <is>
@@ -1680,8 +1700,18 @@
     <mergeCell ref="A5:G5"/>
     <mergeCell ref="A10:G10"/>
   </mergeCells>
-  <pageMargins bottom="1" footer="0.5" header="0.5" left="0.75" right="0.75" top="1"/>
-  <pageSetup fitToHeight="0" fitToWidth="1" orientation="portrait" paperSize="9"/>
+  <conditionalFormatting sqref="A5:G16">
+    <cfRule type="expression" priority="1" dxfId="0">
+      <formula>$F5="✓"</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <dataValidations count="1">
+    <dataValidation sqref="F6 F7 F8 F9 F11 F12 F13 F14 F15 F16" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+      <formula1>"✓,—,N/A"</formula1>
+    </dataValidation>
+  </dataValidations>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <pageSetup orientation="portrait" paperSize="9" fitToHeight="0" fitToWidth="1"/>
 </worksheet>
 </file>
 
@@ -1695,16 +1725,16 @@
   <dimension ref="A1:G29"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col customWidth="1" max="1" min="1" width="4"/>
-    <col customWidth="1" max="2" min="2" width="45"/>
-    <col customWidth="1" max="3" min="3" width="14"/>
-    <col customWidth="1" max="4" min="4" width="18"/>
-    <col customWidth="1" max="5" min="5" width="12"/>
-    <col customWidth="1" max="6" min="6" width="8"/>
-    <col customWidth="1" max="7" min="7" width="12"/>
+    <col width="4" customWidth="1" min="1" max="1"/>
+    <col width="45" customWidth="1" min="2" max="2"/>
+    <col width="14" customWidth="1" min="3" max="3"/>
+    <col width="18" customWidth="1" min="4" max="4"/>
+    <col width="12" customWidth="1" min="5" max="5"/>
+    <col width="8" customWidth="1" min="6" max="6"/>
+    <col width="12" customWidth="1" min="7" max="7"/>
   </cols>
   <sheetData>
-    <row customHeight="1" ht="30" r="1">
+    <row r="1" ht="30" customHeight="1">
       <c r="A1" s="4" t="inlineStr">
         <is>
           <t>Tareas Específicas — Navidad y Festivos de Invierno</t>
@@ -1718,10 +1748,11 @@
         </is>
       </c>
     </row>
+    <row r="3"/>
     <row r="4">
       <c r="A4" s="6" t="inlineStr">
         <is>
-          <t>☐</t>
+          <t>Nº</t>
         </is>
       </c>
       <c r="B4" s="6" t="inlineStr">
@@ -1746,7 +1777,7 @@
       </c>
       <c r="F4" s="6" t="inlineStr">
         <is>
-          <t>Hecha</t>
+          <t>✓ Completada</t>
         </is>
       </c>
       <c r="G4" s="6" t="inlineStr">
@@ -1763,10 +1794,8 @@
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="8" t="inlineStr">
-        <is>
-          <t>☐</t>
-        </is>
+      <c r="A6" s="20" t="n">
+        <v>1</v>
       </c>
       <c r="B6" s="9" t="inlineStr">
         <is>
@@ -1792,10 +1821,8 @@
       <c r="G6" s="11" t="n"/>
     </row>
     <row r="7">
-      <c r="A7" s="12" t="inlineStr">
-        <is>
-          <t>☐</t>
-        </is>
+      <c r="A7" s="21" t="n">
+        <v>2</v>
       </c>
       <c r="B7" s="13" t="inlineStr">
         <is>
@@ -1821,10 +1848,8 @@
       <c r="G7" s="15" t="n"/>
     </row>
     <row r="8">
-      <c r="A8" s="8" t="inlineStr">
-        <is>
-          <t>☐</t>
-        </is>
+      <c r="A8" s="20" t="n">
+        <v>3</v>
       </c>
       <c r="B8" s="9" t="inlineStr">
         <is>
@@ -1850,10 +1875,8 @@
       <c r="G8" s="11" t="n"/>
     </row>
     <row r="9">
-      <c r="A9" s="12" t="inlineStr">
-        <is>
-          <t>☐</t>
-        </is>
+      <c r="A9" s="21" t="n">
+        <v>4</v>
       </c>
       <c r="B9" s="13" t="inlineStr">
         <is>
@@ -1886,10 +1909,8 @@
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="12" t="inlineStr">
-        <is>
-          <t>☐</t>
-        </is>
+      <c r="A11" s="21" t="n">
+        <v>5</v>
       </c>
       <c r="B11" s="13" t="inlineStr">
         <is>
@@ -1915,10 +1936,8 @@
       <c r="G11" s="15" t="n"/>
     </row>
     <row r="12">
-      <c r="A12" s="8" t="inlineStr">
-        <is>
-          <t>☐</t>
-        </is>
+      <c r="A12" s="20" t="n">
+        <v>6</v>
       </c>
       <c r="B12" s="9" t="inlineStr">
         <is>
@@ -1944,10 +1963,8 @@
       <c r="G12" s="11" t="n"/>
     </row>
     <row r="13">
-      <c r="A13" s="12" t="inlineStr">
-        <is>
-          <t>☐</t>
-        </is>
+      <c r="A13" s="21" t="n">
+        <v>7</v>
       </c>
       <c r="B13" s="13" t="inlineStr">
         <is>
@@ -1980,10 +1997,8 @@
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="12" t="inlineStr">
-        <is>
-          <t>☐</t>
-        </is>
+      <c r="A15" s="21" t="n">
+        <v>8</v>
       </c>
       <c r="B15" s="13" t="inlineStr">
         <is>
@@ -2009,10 +2024,8 @@
       <c r="G15" s="15" t="n"/>
     </row>
     <row r="16">
-      <c r="A16" s="8" t="inlineStr">
-        <is>
-          <t>☐</t>
-        </is>
+      <c r="A16" s="20" t="n">
+        <v>9</v>
       </c>
       <c r="B16" s="9" t="inlineStr">
         <is>
@@ -2038,10 +2051,8 @@
       <c r="G16" s="11" t="n"/>
     </row>
     <row r="17">
-      <c r="A17" s="12" t="inlineStr">
-        <is>
-          <t>☐</t>
-        </is>
+      <c r="A17" s="21" t="n">
+        <v>10</v>
       </c>
       <c r="B17" s="13" t="inlineStr">
         <is>
@@ -2067,10 +2078,8 @@
       <c r="G17" s="15" t="n"/>
     </row>
     <row r="18">
-      <c r="A18" s="8" t="inlineStr">
-        <is>
-          <t>☐</t>
-        </is>
+      <c r="A18" s="20" t="n">
+        <v>11</v>
       </c>
       <c r="B18" s="9" t="inlineStr">
         <is>
@@ -2096,10 +2105,8 @@
       <c r="G18" s="11" t="n"/>
     </row>
     <row r="19">
-      <c r="A19" s="12" t="inlineStr">
-        <is>
-          <t>☐</t>
-        </is>
+      <c r="A19" s="21" t="n">
+        <v>12</v>
       </c>
       <c r="B19" s="13" t="inlineStr">
         <is>
@@ -2132,10 +2139,8 @@
       </c>
     </row>
     <row r="21">
-      <c r="A21" s="12" t="inlineStr">
-        <is>
-          <t>☐</t>
-        </is>
+      <c r="A21" s="21" t="n">
+        <v>13</v>
       </c>
       <c r="B21" s="13" t="inlineStr">
         <is>
@@ -2161,10 +2166,8 @@
       <c r="G21" s="15" t="n"/>
     </row>
     <row r="22">
-      <c r="A22" s="8" t="inlineStr">
-        <is>
-          <t>☐</t>
-        </is>
+      <c r="A22" s="20" t="n">
+        <v>14</v>
       </c>
       <c r="B22" s="9" t="inlineStr">
         <is>
@@ -2190,10 +2193,8 @@
       <c r="G22" s="11" t="n"/>
     </row>
     <row r="23">
-      <c r="A23" s="12" t="inlineStr">
-        <is>
-          <t>☐</t>
-        </is>
+      <c r="A23" s="21" t="n">
+        <v>15</v>
       </c>
       <c r="B23" s="13" t="inlineStr">
         <is>
@@ -2218,6 +2219,7 @@
       <c r="F23" s="15" t="n"/>
       <c r="G23" s="15" t="n"/>
     </row>
+    <row r="24"/>
     <row r="25">
       <c r="C25" s="16" t="inlineStr">
         <is>
@@ -2226,14 +2228,19 @@
       </c>
       <c r="D25" s="17">
         <f>COUNTIF(F5:F23,"✓")</f>
-        <v/>
+        <v>0.0</v>
       </c>
       <c r="E25" s="16" t="inlineStr">
         <is>
-          <t>de 15</t>
-        </is>
-      </c>
-    </row>
+          <t>de</t>
+        </is>
+      </c>
+      <c r="F25">
+        <f>COUNTIF(B5:B23,"?*")</f>
+        <v>15.0</v>
+      </c>
+    </row>
+    <row r="26"/>
     <row r="27">
       <c r="A27" s="18" t="inlineStr">
         <is>
@@ -2241,6 +2248,7 @@
         </is>
       </c>
     </row>
+    <row r="28"/>
     <row r="29">
       <c r="A29" s="19" t="inlineStr">
         <is>
@@ -2259,8 +2267,18 @@
     <mergeCell ref="A29:G29"/>
     <mergeCell ref="A10:G10"/>
   </mergeCells>
-  <pageMargins bottom="1" footer="0.5" header="0.5" left="0.75" right="0.75" top="1"/>
-  <pageSetup fitToHeight="0" fitToWidth="1" orientation="portrait" paperSize="9"/>
+  <conditionalFormatting sqref="A5:G23">
+    <cfRule type="expression" priority="1" dxfId="0">
+      <formula>$F5="✓"</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <dataValidations count="1">
+    <dataValidation sqref="F6 F7 F8 F9 F11 F12 F13 F15 F16 F17 F18 F19 F21 F22 F23" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+      <formula1>"✓,—,N/A"</formula1>
+    </dataValidation>
+  </dataValidations>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <pageSetup orientation="portrait" paperSize="9" fitToHeight="0" fitToWidth="1"/>
 </worksheet>
 </file>
 
@@ -2274,16 +2292,16 @@
   <dimension ref="A1:G24"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col customWidth="1" max="1" min="1" width="4"/>
-    <col customWidth="1" max="2" min="2" width="45"/>
-    <col customWidth="1" max="3" min="3" width="14"/>
-    <col customWidth="1" max="4" min="4" width="18"/>
-    <col customWidth="1" max="5" min="5" width="12"/>
-    <col customWidth="1" max="6" min="6" width="8"/>
-    <col customWidth="1" max="7" min="7" width="12"/>
+    <col width="4" customWidth="1" min="1" max="1"/>
+    <col width="45" customWidth="1" min="2" max="2"/>
+    <col width="14" customWidth="1" min="3" max="3"/>
+    <col width="18" customWidth="1" min="4" max="4"/>
+    <col width="12" customWidth="1" min="5" max="5"/>
+    <col width="8" customWidth="1" min="6" max="6"/>
+    <col width="12" customWidth="1" min="7" max="7"/>
   </cols>
   <sheetData>
-    <row customHeight="1" ht="30" r="1">
+    <row r="1" ht="30" customHeight="1">
       <c r="A1" s="4" t="inlineStr">
         <is>
           <t>Tareas de Inicio / Fin de Temporada de Terraza</t>
@@ -2297,10 +2315,11 @@
         </is>
       </c>
     </row>
+    <row r="3"/>
     <row r="4">
       <c r="A4" s="6" t="inlineStr">
         <is>
-          <t>☐</t>
+          <t>Nº</t>
         </is>
       </c>
       <c r="B4" s="6" t="inlineStr">
@@ -2325,7 +2344,7 @@
       </c>
       <c r="F4" s="6" t="inlineStr">
         <is>
-          <t>Hecha</t>
+          <t>✓ Completada</t>
         </is>
       </c>
       <c r="G4" s="6" t="inlineStr">
@@ -2342,10 +2361,8 @@
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="8" t="inlineStr">
-        <is>
-          <t>☐</t>
-        </is>
+      <c r="A6" s="20" t="n">
+        <v>1</v>
       </c>
       <c r="B6" s="9" t="inlineStr">
         <is>
@@ -2371,10 +2388,8 @@
       <c r="G6" s="11" t="n"/>
     </row>
     <row r="7">
-      <c r="A7" s="12" t="inlineStr">
-        <is>
-          <t>☐</t>
-        </is>
+      <c r="A7" s="21" t="n">
+        <v>2</v>
       </c>
       <c r="B7" s="13" t="inlineStr">
         <is>
@@ -2400,10 +2415,8 @@
       <c r="G7" s="15" t="n"/>
     </row>
     <row r="8">
-      <c r="A8" s="8" t="inlineStr">
-        <is>
-          <t>☐</t>
-        </is>
+      <c r="A8" s="20" t="n">
+        <v>3</v>
       </c>
       <c r="B8" s="9" t="inlineStr">
         <is>
@@ -2429,10 +2442,8 @@
       <c r="G8" s="11" t="n"/>
     </row>
     <row r="9">
-      <c r="A9" s="12" t="inlineStr">
-        <is>
-          <t>☐</t>
-        </is>
+      <c r="A9" s="21" t="n">
+        <v>4</v>
       </c>
       <c r="B9" s="13" t="inlineStr">
         <is>
@@ -2458,10 +2469,8 @@
       <c r="G9" s="15" t="n"/>
     </row>
     <row r="10">
-      <c r="A10" s="8" t="inlineStr">
-        <is>
-          <t>☐</t>
-        </is>
+      <c r="A10" s="20" t="n">
+        <v>5</v>
       </c>
       <c r="B10" s="9" t="inlineStr">
         <is>
@@ -2487,10 +2496,8 @@
       <c r="G10" s="11" t="n"/>
     </row>
     <row r="11">
-      <c r="A11" s="12" t="inlineStr">
-        <is>
-          <t>☐</t>
-        </is>
+      <c r="A11" s="21" t="n">
+        <v>6</v>
       </c>
       <c r="B11" s="13" t="inlineStr">
         <is>
@@ -2516,10 +2523,8 @@
       <c r="G11" s="15" t="n"/>
     </row>
     <row r="12">
-      <c r="A12" s="8" t="inlineStr">
-        <is>
-          <t>☐</t>
-        </is>
+      <c r="A12" s="20" t="n">
+        <v>7</v>
       </c>
       <c r="B12" s="9" t="inlineStr">
         <is>
@@ -2552,10 +2557,8 @@
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="8" t="inlineStr">
-        <is>
-          <t>☐</t>
-        </is>
+      <c r="A14" s="20" t="n">
+        <v>8</v>
       </c>
       <c r="B14" s="9" t="inlineStr">
         <is>
@@ -2581,10 +2584,8 @@
       <c r="G14" s="11" t="n"/>
     </row>
     <row r="15">
-      <c r="A15" s="12" t="inlineStr">
-        <is>
-          <t>☐</t>
-        </is>
+      <c r="A15" s="21" t="n">
+        <v>9</v>
       </c>
       <c r="B15" s="13" t="inlineStr">
         <is>
@@ -2610,10 +2611,8 @@
       <c r="G15" s="15" t="n"/>
     </row>
     <row r="16">
-      <c r="A16" s="8" t="inlineStr">
-        <is>
-          <t>☐</t>
-        </is>
+      <c r="A16" s="20" t="n">
+        <v>10</v>
       </c>
       <c r="B16" s="9" t="inlineStr">
         <is>
@@ -2639,10 +2638,8 @@
       <c r="G16" s="11" t="n"/>
     </row>
     <row r="17">
-      <c r="A17" s="12" t="inlineStr">
-        <is>
-          <t>☐</t>
-        </is>
+      <c r="A17" s="21" t="n">
+        <v>11</v>
       </c>
       <c r="B17" s="13" t="inlineStr">
         <is>
@@ -2668,10 +2665,8 @@
       <c r="G17" s="15" t="n"/>
     </row>
     <row r="18">
-      <c r="A18" s="8" t="inlineStr">
-        <is>
-          <t>☐</t>
-        </is>
+      <c r="A18" s="20" t="n">
+        <v>12</v>
       </c>
       <c r="B18" s="9" t="inlineStr">
         <is>
@@ -2696,6 +2691,7 @@
       <c r="F18" s="11" t="n"/>
       <c r="G18" s="11" t="n"/>
     </row>
+    <row r="19"/>
     <row r="20">
       <c r="C20" s="16" t="inlineStr">
         <is>
@@ -2704,14 +2700,19 @@
       </c>
       <c r="D20" s="17">
         <f>COUNTIF(F5:F18,"✓")</f>
-        <v/>
+        <v>0.0</v>
       </c>
       <c r="E20" s="16" t="inlineStr">
         <is>
-          <t>de 12</t>
-        </is>
-      </c>
-    </row>
+          <t>de</t>
+        </is>
+      </c>
+      <c r="F20">
+        <f>COUNTIF(B5:B18,"?*")</f>
+        <v>12.0</v>
+      </c>
+    </row>
+    <row r="21"/>
     <row r="22">
       <c r="A22" s="18" t="inlineStr">
         <is>
@@ -2719,6 +2720,7 @@
         </is>
       </c>
     </row>
+    <row r="23"/>
     <row r="24">
       <c r="A24" s="19" t="inlineStr">
         <is>
@@ -2735,7 +2737,17 @@
     <mergeCell ref="A5:G5"/>
     <mergeCell ref="A22:G22"/>
   </mergeCells>
-  <pageMargins bottom="1" footer="0.5" header="0.5" left="0.75" right="0.75" top="1"/>
-  <pageSetup fitToHeight="0" fitToWidth="1" orientation="portrait" paperSize="9"/>
+  <conditionalFormatting sqref="A5:G18">
+    <cfRule type="expression" priority="1" dxfId="0">
+      <formula>$F5="✓"</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <dataValidations count="1">
+    <dataValidation sqref="F6 F7 F8 F9 F10 F11 F12 F14 F15 F16 F17 F18" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+      <formula1>"✓,—,N/A"</formula1>
+    </dataValidation>
+  </dataValidations>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <pageSetup orientation="portrait" paperSize="9" fitToHeight="0" fitToWidth="1"/>
 </worksheet>
 </file>
--- a/astro-site/public/dl/kit-tareas-cafeteria/06-eventos-festivos.xlsx
+++ b/astro-site/public/dl/kit-tareas-cafeteria/06-eventos-festivos.xlsx
@@ -14,9 +14,13 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Temporada Terraza" sheetId="5" state="visible" r:id="rId5"/>
   </sheets>
   <definedNames>
+    <definedName name="_xlnm.Print_Titles" localSheetId="1">'Brunch Dominical'!$4:$4</definedName>
     <definedName name="_xlnm.Print_Area" localSheetId="1">'Brunch Dominical'!$A$1:$G$32</definedName>
+    <definedName name="_xlnm.Print_Titles" localSheetId="2">'San Valentín'!$4:$4</definedName>
     <definedName name="_xlnm.Print_Area" localSheetId="2">'San Valentín'!$A$1:$G$22</definedName>
+    <definedName name="_xlnm.Print_Titles" localSheetId="3">'Navidad'!$4:$4</definedName>
     <definedName name="_xlnm.Print_Area" localSheetId="3">'Navidad'!$A$1:$G$29</definedName>
+    <definedName name="_xlnm.Print_Titles" localSheetId="4">'Temporada Terraza'!$4:$4</definedName>
     <definedName name="_xlnm.Print_Area" localSheetId="4">'Temporada Terraza'!$A$1:$G$24</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -656,7 +660,7 @@
   <sheetPr>
     <tabColor rgb="00FF6600"/>
     <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
+    <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:G32"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
@@ -1294,8 +1298,16 @@
       <formula1>"✓,—,N/A"</formula1>
     </dataValidation>
   </dataValidations>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <pageMargins left="0.59" right="0.59" top="0.59" bottom="0.59" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" paperSize="9" fitToHeight="0" fitToWidth="1"/>
+  <headerFooter>
+    <oddHeader/>
+    <oddFooter>&amp;C&amp;8 AI Chef Pro · aichef.pro · Página &amp;P de &amp;N</oddFooter>
+    <evenHeader/>
+    <evenFooter/>
+    <firstHeader/>
+    <firstFooter/>
+  </headerFooter>
 </worksheet>
 </file>
 
@@ -1304,7 +1316,7 @@
   <sheetPr>
     <tabColor rgb="00C00000"/>
     <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
+    <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:G22"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
@@ -1710,8 +1722,16 @@
       <formula1>"✓,—,N/A"</formula1>
     </dataValidation>
   </dataValidations>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <pageMargins left="0.59" right="0.59" top="0.59" bottom="0.59" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" paperSize="9" fitToHeight="0" fitToWidth="1"/>
+  <headerFooter>
+    <oddHeader/>
+    <oddFooter>&amp;C&amp;8 AI Chef Pro · aichef.pro · Página &amp;P de &amp;N</oddFooter>
+    <evenHeader/>
+    <evenFooter/>
+    <firstHeader/>
+    <firstFooter/>
+  </headerFooter>
 </worksheet>
 </file>
 
@@ -1720,7 +1740,7 @@
   <sheetPr>
     <tabColor rgb="00228B22"/>
     <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
+    <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:G29"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
@@ -2277,8 +2297,16 @@
       <formula1>"✓,—,N/A"</formula1>
     </dataValidation>
   </dataValidations>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <pageMargins left="0.59" right="0.59" top="0.59" bottom="0.59" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" paperSize="9" fitToHeight="0" fitToWidth="1"/>
+  <headerFooter>
+    <oddHeader/>
+    <oddFooter>&amp;C&amp;8 AI Chef Pro · aichef.pro · Página &amp;P de &amp;N</oddFooter>
+    <evenHeader/>
+    <evenFooter/>
+    <firstHeader/>
+    <firstFooter/>
+  </headerFooter>
 </worksheet>
 </file>
 
@@ -2287,7 +2315,7 @@
   <sheetPr>
     <tabColor rgb="004472C4"/>
     <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
+    <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:G24"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
@@ -2747,7 +2775,15 @@
       <formula1>"✓,—,N/A"</formula1>
     </dataValidation>
   </dataValidations>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <pageMargins left="0.59" right="0.59" top="0.59" bottom="0.59" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" paperSize="9" fitToHeight="0" fitToWidth="1"/>
+  <headerFooter>
+    <oddHeader/>
+    <oddFooter>&amp;C&amp;8 AI Chef Pro · aichef.pro · Página &amp;P de &amp;N</oddFooter>
+    <evenHeader/>
+    <evenFooter/>
+    <firstHeader/>
+    <firstFooter/>
+  </headerFooter>
 </worksheet>
 </file>
--- a/astro-site/public/dl/kit-tareas-cafeteria/06-eventos-festivos.xlsx
+++ b/astro-site/public/dl/kit-tareas-cafeteria/06-eventos-festivos.xlsx
@@ -14,14 +14,15 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Temporada Terraza" sheetId="5" state="visible" r:id="rId5"/>
   </sheets>
   <definedNames>
+    <definedName name="_xlnm.Print_Area" localSheetId="0">'Instrucciones'!$A$1:$B$33</definedName>
     <definedName name="_xlnm.Print_Titles" localSheetId="1">'Brunch Dominical'!$4:$4</definedName>
-    <definedName name="_xlnm.Print_Area" localSheetId="1">'Brunch Dominical'!$A$1:$G$32</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="1">'Brunch Dominical'!$A$1:$G$38</definedName>
     <definedName name="_xlnm.Print_Titles" localSheetId="2">'San Valentín'!$4:$4</definedName>
-    <definedName name="_xlnm.Print_Area" localSheetId="2">'San Valentín'!$A$1:$G$22</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="2">'San Valentín'!$A$1:$G$28</definedName>
     <definedName name="_xlnm.Print_Titles" localSheetId="3">'Navidad'!$4:$4</definedName>
-    <definedName name="_xlnm.Print_Area" localSheetId="3">'Navidad'!$A$1:$G$29</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="3">'Navidad'!$A$1:$G$34</definedName>
     <definedName name="_xlnm.Print_Titles" localSheetId="4">'Temporada Terraza'!$4:$4</definedName>
-    <definedName name="_xlnm.Print_Area" localSheetId="4">'Temporada Terraza'!$A$1:$G$24</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="4">'Temporada Terraza'!$A$1:$G$29</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -30,7 +31,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="12">
+  <fonts count="15">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -94,8 +95,22 @@
       <color rgb="00666666"/>
       <sz val="10"/>
     </font>
+    <font>
+      <b val="1"/>
+      <color rgb="00FFD700"/>
+      <sz val="18"/>
+    </font>
+    <font>
+      <b val="1"/>
+      <color rgb="00333333"/>
+      <sz val="12"/>
+    </font>
+    <font>
+      <color rgb="00555555"/>
+      <sz val="11"/>
+    </font>
   </fonts>
-  <fills count="6">
+  <fills count="7">
     <fill>
       <patternFill/>
     </fill>
@@ -126,6 +141,11 @@
         <bgColor rgb="00FFFFFF"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00E8F5E9"/>
+      </patternFill>
+    </fill>
   </fills>
   <borders count="2">
     <border>
@@ -153,7 +173,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="22">
+  <cellXfs count="35">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -195,6 +215,50 @@
     </xf>
     <xf numFmtId="0" fontId="11" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="0" applyAlignment="1" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center"/>
+      <protection locked="0" hidden="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <protection locked="0" hidden="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="4" borderId="1" applyAlignment="1" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0" hidden="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="4" borderId="1" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <protection locked="0" hidden="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="6" borderId="1" applyAlignment="1" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center"/>
+      <protection locked="0" hidden="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="1" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <protection locked="0" hidden="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="5" borderId="1" applyAlignment="1" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0" hidden="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="5" borderId="1" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <protection locked="0" hidden="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="6" borderId="1" applyAlignment="1" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0" hidden="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="6" borderId="1" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <protection locked="0" hidden="0"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -572,72 +636,165 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:B14"/>
+  <dimension ref="A1:B33"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="4" customWidth="1" min="1" max="1"/>
-    <col width="80" customWidth="1" min="2" max="2"/>
+    <col width="3" customWidth="1" min="1" max="1"/>
+    <col width="100" customWidth="1" min="2" max="2"/>
   </cols>
   <sheetData>
     <row r="1"/>
-    <row r="2">
-      <c r="B2" s="1" t="inlineStr">
+    <row r="2" ht="26" customHeight="1">
+      <c r="B2" s="22" t="inlineStr">
         <is>
           <t>Tareas para Eventos y Festivos — Cafetería / Brunch</t>
         </is>
       </c>
     </row>
     <row r="3"/>
-    <row r="4">
-      <c r="B4" s="2" t="inlineStr">
-        <is>
-          <t>Checklists para los eventos y fechas especiales de tu cafetería.</t>
+    <row r="4" ht="18" customHeight="1">
+      <c r="B4" s="23" t="inlineStr">
+        <is>
+          <t>Cómo cuenta el contador</t>
         </is>
       </c>
     </row>
     <row r="5"/>
-    <row r="6">
-      <c r="B6" s="2" t="inlineStr">
-        <is>
-          <t>• Brunch Dominical: para cuando ofreces brunch especial de fin de semana</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="B7" s="2" t="inlineStr">
-        <is>
-          <t>• San Valentín y Navidad: tareas de preparación y servicio especial</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="B8" s="2" t="inlineStr">
-        <is>
-          <t>• Temporada Terraza: montaje de primavera y recogida de otoño</t>
+    <row r="6" ht="32" customHeight="1">
+      <c r="B6" s="24" t="inlineStr">
+        <is>
+          <t>▸ Marca con ✓ en la columna «✓ Completada» (desplegable): es la que cuenta el total de tareas completadas.</t>
+        </is>
+      </c>
+    </row>
+    <row r="7" ht="32" customHeight="1">
+      <c r="B7" s="24" t="inlineStr">
+        <is>
+          <t>▸ «N/A» = no aplica en tu local: esa tarea SALE del total (no la borres, márcala N/A). «—» = no hecha: sigue contando como pendiente y baja el porcentaje, que es de lo que se trata.</t>
+        </is>
+      </c>
+    </row>
+    <row r="8" ht="32" customHeight="1">
+      <c r="B8" s="24" t="inlineStr">
+        <is>
+          <t>▸ El denominador cuenta las tareas escritas en la columna «Tarea», no un número fijo: si añades o borras tareas, el total se ajusta solo.</t>
         </is>
       </c>
     </row>
     <row r="9"/>
-    <row r="10">
-      <c r="B10" s="3" t="inlineStr">
-        <is>
-          <t>Formato: ☐ = tarea pendiente · ✓ = completada (escribe en columna 'Hecha')</t>
+    <row r="10" ht="18" customHeight="1">
+      <c r="B10" s="23" t="inlineStr">
+        <is>
+          <t>Filas libres</t>
         </is>
       </c>
     </row>
     <row r="11"/>
-    <row r="12">
-      <c r="B12" s="3" t="inlineStr">
-        <is>
-          <t>Marca con ✓ en la columna «✓ Completada» (desplegable): es la que cuenta el total de tareas completadas.</t>
-        </is>
-      </c>
-    </row>
-    <row r="13"/>
+    <row r="12" ht="32" customHeight="1">
+      <c r="B12" s="24" t="inlineStr">
+        <is>
+          <t>▸ Al final de cada tabla hay 5 filas verdes libres DENTRO del rango que cuenta el contador: escribe ahí tus tareas propias.</t>
+        </is>
+      </c>
+    </row>
+    <row r="13" ht="32" customHeight="1">
+      <c r="B13" s="24" t="inlineStr">
+        <is>
+          <t>▸ Si necesitas más, inserta filas DENTRO de la tabla (clic derecho → Insertar), nunca por debajo de la última: lo que se escriba fuera del rango no lo cuenta nadie.</t>
+        </is>
+      </c>
+    </row>
     <row r="14">
-      <c r="B14" s="3" t="inlineStr">
-        <is>
-          <t>Versión 1.1 · agosto 2026 · aichef.pro/kit-tareas-cafeteria · info@aichef.pro</t>
+      <c r="B14" s="3" t="n"/>
+    </row>
+    <row r="15" ht="18" customHeight="1">
+      <c r="B15" s="23" t="inlineStr">
+        <is>
+          <t>Protección de la hoja</t>
+        </is>
+      </c>
+    </row>
+    <row r="17" ht="32" customHeight="1">
+      <c r="B17" s="24" t="inlineStr">
+        <is>
+          <t>▸ Las hojas con fórmulas van protegidas SIN contraseña: las celdas de entrada (las verdes) están desbloqueadas y los cálculos no se pisan por accidente.</t>
+        </is>
+      </c>
+    </row>
+    <row r="18" ht="32" customHeight="1">
+      <c r="B18" s="24" t="inlineStr">
+        <is>
+          <t>▸ Puedes insertar y borrar filas con la protección puesta. Para cambiar la estructura: Revisar → Desproteger hoja.</t>
+        </is>
+      </c>
+    </row>
+    <row r="20" ht="18" customHeight="1">
+      <c r="B20" s="23" t="inlineStr">
+        <is>
+          <t>Se conecta con</t>
+        </is>
+      </c>
+    </row>
+    <row r="22" ht="16" customHeight="1">
+      <c r="B22" s="24" t="inlineStr">
+        <is>
+          <t>▸ 08-apertura-cierre-negocio.xlsx — checklist del LOCAL completo: es el MARCO del día.</t>
+        </is>
+      </c>
+    </row>
+    <row r="23" ht="16" customHeight="1">
+      <c r="B23" s="24" t="inlineStr">
+        <is>
+          <t>▸ 01-apertura-cierre.xlsx — el mismo día con el DETALLE por área (cocina, sala, barra café).</t>
+        </is>
+      </c>
+    </row>
+    <row r="24" ht="16" customHeight="1">
+      <c r="B24" s="24" t="inlineStr">
+        <is>
+          <t>▸ 09-apertura-cierre-caja.xlsx — la CAJA: fondo, recuento por denominaciones, Z del TPV y descuadre.</t>
+        </is>
+      </c>
+    </row>
+    <row r="25" ht="48" customHeight="1">
+      <c r="B25" s="24" t="inlineStr">
+        <is>
+          <t>▸ Orden de uso: local → áreas → caja. Cada fichero cubre un nivel: el de negocio marca el HITO (encender, abrir, cerrar), el de áreas detalla CÓMO se hace en cada zona y el de caja lleva el DINERO. Si una tarea aparece en dos, es a propósito: una es el hito y la otra el detalle.</t>
+        </is>
+      </c>
+    </row>
+    <row r="26" ht="32" customHeight="1">
+      <c r="B26" s="24" t="inlineStr">
+        <is>
+          <t>▸ Estás en 06-eventos-festivos.xlsx: es una capa MÁS, no una repetición — el marco del día está en 08-apertura-cierre-negocio.xlsx y 01-apertura-cierre.xlsx.</t>
+        </is>
+      </c>
+    </row>
+    <row r="28" ht="18" customHeight="1">
+      <c r="B28" s="23" t="inlineStr">
+        <is>
+          <t>— Kit de Tareas Recurrentes · Cafetería / Brunch · AI Chef Pro · aichef.pro</t>
+        </is>
+      </c>
+    </row>
+    <row r="30" ht="35" customHeight="1">
+      <c r="B30" s="23" t="inlineStr">
+        <is>
+          <t>Diseñado por John Guerrero — chef y consultor gastronómico desde 2010, en cocina desde los 17 años · johnguerrero.es</t>
+        </is>
+      </c>
+    </row>
+    <row r="31" ht="18" customHeight="1">
+      <c r="B31" s="23" t="inlineStr">
+        <is>
+          <t>Contacto: info@aichef.pro</t>
+        </is>
+      </c>
+    </row>
+    <row r="33" ht="18" customHeight="1">
+      <c r="B33" s="23" t="inlineStr">
+        <is>
+          <t>Versión 2.0 · agosto 2026 · aichef.pro/kit-tareas-cafeteria · info@aichef.pro</t>
         </is>
       </c>
     </row>
@@ -662,7 +819,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:G32"/>
+  <dimension ref="A1:G38"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="4" customWidth="1" min="1" max="1"/>
@@ -684,7 +841,7 @@
     <row r="2">
       <c r="A2" s="5" t="inlineStr">
         <is>
-          <t>Fecha: ___/___/______    Turno: ☐ Mañana  ☐ Tarde  ☐ Noche    Responsable: ________________</t>
+          <t>Semana del ___/___/______ al ___/___/______    Responsable: _________________________</t>
         </is>
       </c>
     </row>
@@ -712,7 +869,7 @@
       </c>
       <c r="E4" s="6" t="inlineStr">
         <is>
-          <t>Hora Límite</t>
+          <t>Día</t>
         </is>
       </c>
       <c r="F4" s="6" t="inlineStr">
@@ -727,574 +884,672 @@
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="7" t="inlineStr">
+      <c r="A5" s="25" t="inlineStr">
         <is>
           <t xml:space="preserve">  PREPARACIÓN (SÁBADO / PRE-BRUNCH)</t>
         </is>
       </c>
+      <c r="B5" s="26" t="n"/>
+      <c r="C5" s="26" t="n"/>
+      <c r="D5" s="26" t="n"/>
+      <c r="E5" s="26" t="n"/>
+      <c r="F5" s="26" t="n"/>
+      <c r="G5" s="26" t="n"/>
     </row>
     <row r="6">
-      <c r="A6" s="20" t="n">
+      <c r="A6" s="27" t="n">
         <v>1</v>
       </c>
-      <c r="B6" s="9" t="inlineStr">
+      <c r="B6" s="28" t="inlineStr">
         <is>
           <t>Confirmar reservas de brunch del domingo</t>
         </is>
       </c>
-      <c r="C6" s="10" t="inlineStr">
+      <c r="C6" s="29" t="inlineStr">
         <is>
           <t>Office</t>
         </is>
       </c>
-      <c r="D6" s="10" t="inlineStr">
+      <c r="D6" s="29" t="inlineStr">
         <is>
           <t>Manager</t>
         </is>
       </c>
-      <c r="E6" s="10" t="inlineStr">
+      <c r="E6" s="29" t="inlineStr">
         <is>
           <t>Sábado</t>
         </is>
       </c>
-      <c r="F6" s="11" t="n"/>
-      <c r="G6" s="11" t="n"/>
+      <c r="F6" s="30" t="n"/>
+      <c r="G6" s="30" t="n"/>
     </row>
     <row r="7">
-      <c r="A7" s="21" t="n">
+      <c r="A7" s="27" t="n">
         <v>2</v>
       </c>
-      <c r="B7" s="13" t="inlineStr">
+      <c r="B7" s="28" t="inlineStr">
+        <is>
+          <t>Al confirmar cada reserva, anotar POR ESCRITO alérgenos, intolerancias y número real de comensales, y pasarlo a cocina y a barra</t>
+        </is>
+      </c>
+      <c r="C7" s="29" t="inlineStr">
+        <is>
+          <t>Office</t>
+        </is>
+      </c>
+      <c r="D7" s="29" t="inlineStr">
+        <is>
+          <t>Manager</t>
+        </is>
+      </c>
+      <c r="E7" s="29" t="inlineStr">
+        <is>
+          <t>Sábado</t>
+        </is>
+      </c>
+      <c r="F7" s="30" t="n"/>
+      <c r="G7" s="30" t="n"/>
+    </row>
+    <row r="8">
+      <c r="A8" s="31" t="n">
+        <v>3</v>
+      </c>
+      <c r="B8" s="32" t="inlineStr">
         <is>
           <t>Hacer pedido extra: huevos, aguacate, salmón, fruta</t>
         </is>
       </c>
-      <c r="C7" s="14" t="inlineStr">
+      <c r="C8" s="29" t="inlineStr">
         <is>
           <t>Office</t>
         </is>
       </c>
-      <c r="D7" s="14" t="inlineStr">
+      <c r="D8" s="29" t="inlineStr">
         <is>
           <t>Manager</t>
         </is>
       </c>
-      <c r="E7" s="14" t="inlineStr">
+      <c r="E8" s="29" t="inlineStr">
         <is>
           <t>Viernes</t>
         </is>
       </c>
-      <c r="F7" s="15" t="n"/>
-      <c r="G7" s="15" t="n"/>
-    </row>
-    <row r="8">
-      <c r="A8" s="20" t="n">
-        <v>3</v>
-      </c>
-      <c r="B8" s="9" t="inlineStr">
+      <c r="F8" s="30" t="n"/>
+      <c r="G8" s="30" t="n"/>
+    </row>
+    <row r="9">
+      <c r="A9" s="27" t="n">
+        <v>4</v>
+      </c>
+      <c r="B9" s="28" t="inlineStr">
         <is>
           <t>Preparar carta/menú especial de brunch</t>
         </is>
       </c>
-      <c r="C8" s="10" t="inlineStr">
+      <c r="C9" s="29" t="inlineStr">
         <is>
           <t>Office</t>
         </is>
       </c>
-      <c r="D8" s="10" t="inlineStr">
+      <c r="D9" s="29" t="inlineStr">
         <is>
           <t>Manager</t>
         </is>
       </c>
-      <c r="E8" s="10" t="inlineStr">
+      <c r="E9" s="29" t="inlineStr">
         <is>
           <t>Sábado</t>
         </is>
       </c>
-      <c r="F8" s="11" t="n"/>
-      <c r="G8" s="11" t="n"/>
-    </row>
-    <row r="9">
-      <c r="A9" s="21" t="n">
-        <v>4</v>
-      </c>
-      <c r="B9" s="13" t="inlineStr">
+      <c r="F9" s="30" t="n"/>
+      <c r="G9" s="30" t="n"/>
+    </row>
+    <row r="10">
+      <c r="A10" s="31" t="n">
+        <v>5</v>
+      </c>
+      <c r="B10" s="32" t="inlineStr">
         <is>
           <t>Publicar en RRSS: foto + horario de brunch</t>
         </is>
       </c>
-      <c r="C9" s="14" t="inlineStr">
+      <c r="C10" s="29" t="inlineStr">
         <is>
           <t>Office</t>
         </is>
       </c>
-      <c r="D9" s="14" t="inlineStr">
+      <c r="D10" s="29" t="inlineStr">
         <is>
           <t>Manager</t>
         </is>
       </c>
-      <c r="E9" s="14" t="inlineStr">
+      <c r="E10" s="29" t="inlineStr">
         <is>
           <t>Sábado</t>
         </is>
       </c>
-      <c r="F9" s="15" t="n"/>
-      <c r="G9" s="15" t="n"/>
-    </row>
-    <row r="10">
-      <c r="A10" s="20" t="n">
-        <v>5</v>
-      </c>
-      <c r="B10" s="9" t="inlineStr">
+      <c r="F10" s="30" t="n"/>
+      <c r="G10" s="30" t="n"/>
+    </row>
+    <row r="11">
+      <c r="A11" s="27" t="n">
+        <v>6</v>
+      </c>
+      <c r="B11" s="28" t="inlineStr">
         <is>
           <t>Verificar stock extra de café y leches</t>
         </is>
       </c>
-      <c r="C10" s="10" t="inlineStr">
+      <c r="C11" s="29" t="inlineStr">
         <is>
           <t>Almacén</t>
         </is>
       </c>
-      <c r="D10" s="10" t="inlineStr">
+      <c r="D11" s="29" t="inlineStr">
         <is>
           <t>Barista</t>
         </is>
       </c>
-      <c r="E10" s="10" t="inlineStr">
+      <c r="E11" s="29" t="inlineStr">
         <is>
           <t>Sábado</t>
         </is>
       </c>
-      <c r="F10" s="11" t="n"/>
-      <c r="G10" s="11" t="n"/>
-    </row>
-    <row r="11">
-      <c r="A11" s="7" t="inlineStr">
+      <c r="F11" s="30" t="n"/>
+      <c r="G11" s="30" t="n"/>
+    </row>
+    <row r="12">
+      <c r="A12" s="25" t="inlineStr">
         <is>
           <t xml:space="preserve">  DOMINGO — APERTURA ESPECIAL</t>
         </is>
       </c>
-    </row>
-    <row r="12">
-      <c r="A12" s="20" t="n">
-        <v>6</v>
-      </c>
-      <c r="B12" s="9" t="inlineStr">
+      <c r="B12" s="26" t="n"/>
+      <c r="C12" s="26" t="n"/>
+      <c r="D12" s="26" t="n"/>
+      <c r="E12" s="26" t="n"/>
+      <c r="F12" s="26" t="n"/>
+      <c r="G12" s="26" t="n"/>
+    </row>
+    <row r="13">
+      <c r="A13" s="27" t="n">
+        <v>7</v>
+      </c>
+      <c r="B13" s="28" t="inlineStr">
         <is>
           <t>Montar buffet de brunch si aplica (zumos, fruta, bollería)</t>
         </is>
       </c>
-      <c r="C12" s="10" t="inlineStr">
+      <c r="C13" s="29" t="inlineStr">
         <is>
           <t>Sala</t>
         </is>
       </c>
-      <c r="D12" s="10" t="inlineStr">
+      <c r="D13" s="29" t="inlineStr">
         <is>
           <t>Camarero/a</t>
         </is>
       </c>
-      <c r="E12" s="10" t="inlineStr">
+      <c r="E13" s="29" t="inlineStr">
         <is>
           <t>08:00</t>
         </is>
       </c>
-      <c r="F12" s="11" t="n"/>
-      <c r="G12" s="11" t="n"/>
-    </row>
-    <row r="13">
-      <c r="A13" s="21" t="n">
-        <v>7</v>
-      </c>
-      <c r="B13" s="13" t="inlineStr">
+      <c r="F13" s="30" t="n"/>
+      <c r="G13" s="30" t="n"/>
+    </row>
+    <row r="14">
+      <c r="A14" s="31" t="n">
+        <v>8</v>
+      </c>
+      <c r="B14" s="32" t="inlineStr">
         <is>
           <t>Decoración especial de mesas (flores, servilletas de tela)</t>
         </is>
       </c>
-      <c r="C13" s="14" t="inlineStr">
+      <c r="C14" s="29" t="inlineStr">
         <is>
           <t>Sala</t>
         </is>
       </c>
-      <c r="D13" s="14" t="inlineStr">
+      <c r="D14" s="29" t="inlineStr">
         <is>
           <t>Camarero/a</t>
         </is>
       </c>
-      <c r="E13" s="14" t="inlineStr">
+      <c r="E14" s="29" t="inlineStr">
         <is>
           <t>08:00</t>
         </is>
       </c>
-      <c r="F13" s="15" t="n"/>
-      <c r="G13" s="15" t="n"/>
-    </row>
-    <row r="14">
-      <c r="A14" s="20" t="n">
-        <v>8</v>
-      </c>
-      <c r="B14" s="9" t="inlineStr">
+      <c r="F14" s="30" t="n"/>
+      <c r="G14" s="30" t="n"/>
+    </row>
+    <row r="15">
+      <c r="A15" s="27" t="n">
+        <v>9</v>
+      </c>
+      <c r="B15" s="28" t="inlineStr">
         <is>
           <t>Preparar doble cantidad de mise en place brunch</t>
         </is>
       </c>
-      <c r="C14" s="10" t="inlineStr">
+      <c r="C15" s="29" t="inlineStr">
         <is>
           <t>Cocina</t>
         </is>
       </c>
-      <c r="D14" s="10" t="inlineStr">
+      <c r="D15" s="29" t="inlineStr">
         <is>
           <t>Cocinero</t>
         </is>
       </c>
-      <c r="E14" s="10" t="inlineStr">
+      <c r="E15" s="29" t="inlineStr">
         <is>
           <t>07:00</t>
         </is>
       </c>
-      <c r="F14" s="11" t="n"/>
-      <c r="G14" s="11" t="n"/>
-    </row>
-    <row r="15">
-      <c r="A15" s="21" t="n">
-        <v>9</v>
-      </c>
-      <c r="B15" s="13" t="inlineStr">
+      <c r="F15" s="30" t="n"/>
+      <c r="G15" s="30" t="n"/>
+    </row>
+    <row r="16">
+      <c r="A16" s="31" t="n">
+        <v>10</v>
+      </c>
+      <c r="B16" s="32" t="inlineStr">
         <is>
           <t>Preparar batch de zumo de naranja natural</t>
         </is>
       </c>
-      <c r="C15" s="14" t="inlineStr">
+      <c r="C16" s="29" t="inlineStr">
         <is>
           <t>Barra</t>
         </is>
       </c>
-      <c r="D15" s="14" t="inlineStr">
+      <c r="D16" s="29" t="inlineStr">
         <is>
           <t>Barista</t>
         </is>
       </c>
-      <c r="E15" s="14" t="inlineStr">
+      <c r="E16" s="29" t="inlineStr">
         <is>
           <t>07:30</t>
         </is>
       </c>
-      <c r="F15" s="15" t="n"/>
-      <c r="G15" s="15" t="n"/>
-    </row>
-    <row r="16">
-      <c r="A16" s="20" t="n">
-        <v>10</v>
-      </c>
-      <c r="B16" s="9" t="inlineStr">
+      <c r="F16" s="30" t="n"/>
+      <c r="G16" s="30" t="n"/>
+    </row>
+    <row r="17">
+      <c r="A17" s="27" t="n">
+        <v>11</v>
+      </c>
+      <c r="B17" s="28" t="inlineStr">
         <is>
           <t>Preparar smoothies base extra</t>
         </is>
       </c>
-      <c r="C16" s="10" t="inlineStr">
+      <c r="C17" s="29" t="inlineStr">
         <is>
           <t>Barra</t>
         </is>
       </c>
-      <c r="D16" s="10" t="inlineStr">
+      <c r="D17" s="29" t="inlineStr">
         <is>
           <t>Barista</t>
         </is>
       </c>
-      <c r="E16" s="10" t="inlineStr">
+      <c r="E17" s="29" t="inlineStr">
         <is>
           <t>07:30</t>
         </is>
       </c>
-      <c r="F16" s="11" t="n"/>
-      <c r="G16" s="11" t="n"/>
-    </row>
-    <row r="17">
-      <c r="A17" s="7" t="inlineStr">
+      <c r="F17" s="30" t="n"/>
+      <c r="G17" s="30" t="n"/>
+    </row>
+    <row r="18">
+      <c r="A18" s="25" t="inlineStr">
         <is>
           <t xml:space="preserve">  DURANTE EL SERVICIO</t>
         </is>
       </c>
-    </row>
-    <row r="18">
-      <c r="A18" s="20" t="n">
-        <v>11</v>
-      </c>
-      <c r="B18" s="9" t="inlineStr">
+      <c r="B18" s="26" t="n"/>
+      <c r="C18" s="26" t="n"/>
+      <c r="D18" s="26" t="n"/>
+      <c r="E18" s="26" t="n"/>
+      <c r="F18" s="26" t="n"/>
+      <c r="G18" s="26" t="n"/>
+    </row>
+    <row r="19">
+      <c r="A19" s="27" t="n">
+        <v>12</v>
+      </c>
+      <c r="B19" s="28" t="inlineStr">
         <is>
           <t>Gestionar cola de espera si hay lleno</t>
         </is>
       </c>
-      <c r="C18" s="10" t="inlineStr">
+      <c r="C19" s="29" t="inlineStr">
         <is>
           <t>Sala</t>
         </is>
       </c>
-      <c r="D18" s="10" t="inlineStr">
+      <c r="D19" s="29" t="inlineStr">
         <is>
           <t>Manager</t>
         </is>
       </c>
-      <c r="E18" s="10" t="inlineStr">
+      <c r="E19" s="29" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="F18" s="11" t="n"/>
-      <c r="G18" s="11" t="n"/>
-    </row>
-    <row r="19">
-      <c r="A19" s="21" t="n">
-        <v>12</v>
-      </c>
-      <c r="B19" s="13" t="inlineStr">
+      <c r="F19" s="30" t="n"/>
+      <c r="G19" s="30" t="n"/>
+    </row>
+    <row r="20">
+      <c r="A20" s="31" t="n">
+        <v>13</v>
+      </c>
+      <c r="B20" s="32" t="inlineStr">
         <is>
           <t>Reponer buffet continuamente</t>
         </is>
       </c>
-      <c r="C19" s="14" t="inlineStr">
+      <c r="C20" s="29" t="inlineStr">
         <is>
           <t>Sala</t>
         </is>
       </c>
-      <c r="D19" s="14" t="inlineStr">
+      <c r="D20" s="29" t="inlineStr">
         <is>
           <t>Camarero/a</t>
         </is>
       </c>
-      <c r="E19" s="14" t="inlineStr">
+      <c r="E20" s="29" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="F19" s="15" t="n"/>
-      <c r="G19" s="15" t="n"/>
-    </row>
-    <row r="20">
-      <c r="A20" s="20" t="n">
-        <v>13</v>
-      </c>
-      <c r="B20" s="9" t="inlineStr">
+      <c r="F20" s="30" t="n"/>
+      <c r="G20" s="30" t="n"/>
+    </row>
+    <row r="21">
+      <c r="A21" s="27" t="n">
+        <v>14</v>
+      </c>
+      <c r="B21" s="28" t="inlineStr">
         <is>
           <t>Reforzar barra: dos baristas si es posible</t>
         </is>
       </c>
-      <c r="C20" s="10" t="inlineStr">
+      <c r="C21" s="29" t="inlineStr">
         <is>
           <t>Barra</t>
         </is>
       </c>
-      <c r="D20" s="10" t="inlineStr">
+      <c r="D21" s="29" t="inlineStr">
         <is>
           <t>Barista</t>
         </is>
       </c>
-      <c r="E20" s="10" t="inlineStr">
+      <c r="E21" s="29" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="F20" s="11" t="n"/>
-      <c r="G20" s="11" t="n"/>
-    </row>
-    <row r="21">
-      <c r="A21" s="21" t="n">
-        <v>14</v>
-      </c>
-      <c r="B21" s="13" t="inlineStr">
+      <c r="F21" s="30" t="n"/>
+      <c r="G21" s="30" t="n"/>
+    </row>
+    <row r="22">
+      <c r="A22" s="31" t="n">
+        <v>15</v>
+      </c>
+      <c r="B22" s="32" t="inlineStr">
         <is>
           <t>Controlar tiempos: brunch no debe tardar +15 min</t>
         </is>
       </c>
-      <c r="C21" s="14" t="inlineStr">
+      <c r="C22" s="29" t="inlineStr">
         <is>
           <t>Cocina</t>
         </is>
       </c>
-      <c r="D21" s="14" t="inlineStr">
+      <c r="D22" s="29" t="inlineStr">
         <is>
           <t>Cocinero</t>
         </is>
       </c>
-      <c r="E21" s="14" t="inlineStr">
+      <c r="E22" s="29" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="F21" s="15" t="n"/>
-      <c r="G21" s="15" t="n"/>
-    </row>
-    <row r="22">
-      <c r="A22" s="20" t="n">
-        <v>15</v>
-      </c>
-      <c r="B22" s="9" t="inlineStr">
+      <c r="F22" s="30" t="n"/>
+      <c r="G22" s="30" t="n"/>
+    </row>
+    <row r="23">
+      <c r="A23" s="27" t="n">
+        <v>16</v>
+      </c>
+      <c r="B23" s="28" t="inlineStr">
         <is>
           <t>Ofrecer mimosa/bellini como extra</t>
         </is>
       </c>
-      <c r="C22" s="10" t="inlineStr">
+      <c r="C23" s="29" t="inlineStr">
         <is>
           <t>Sala</t>
         </is>
       </c>
-      <c r="D22" s="10" t="inlineStr">
+      <c r="D23" s="29" t="inlineStr">
         <is>
           <t>Camarero/a</t>
         </is>
       </c>
-      <c r="E22" s="10" t="inlineStr">
+      <c r="E23" s="29" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="F22" s="11" t="n"/>
-      <c r="G22" s="11" t="n"/>
-    </row>
-    <row r="23">
-      <c r="A23" s="7" t="inlineStr">
+      <c r="F23" s="30" t="n"/>
+      <c r="G23" s="30" t="n"/>
+    </row>
+    <row r="24">
+      <c r="A24" s="25" t="inlineStr">
         <is>
           <t xml:space="preserve">  CIERRE POST-BRUNCH</t>
         </is>
       </c>
-    </row>
-    <row r="24">
-      <c r="A24" s="20" t="n">
-        <v>16</v>
-      </c>
-      <c r="B24" s="9" t="inlineStr">
+      <c r="B24" s="26" t="n"/>
+      <c r="C24" s="26" t="n"/>
+      <c r="D24" s="26" t="n"/>
+      <c r="E24" s="26" t="n"/>
+      <c r="F24" s="26" t="n"/>
+      <c r="G24" s="26" t="n"/>
+    </row>
+    <row r="25">
+      <c r="A25" s="27" t="n">
+        <v>17</v>
+      </c>
+      <c r="B25" s="28" t="inlineStr">
         <is>
           <t>Recoger buffet y guardar sobrantes etiquetados</t>
         </is>
       </c>
-      <c r="C24" s="10" t="inlineStr">
+      <c r="C25" s="29" t="inlineStr">
         <is>
           <t>Sala</t>
         </is>
       </c>
-      <c r="D24" s="10" t="inlineStr">
+      <c r="D25" s="29" t="inlineStr">
         <is>
           <t>Camarero/a</t>
         </is>
       </c>
-      <c r="E24" s="10" t="inlineStr">
+      <c r="E25" s="29" t="inlineStr">
         <is>
           <t>15:00</t>
         </is>
       </c>
-      <c r="F24" s="11" t="n"/>
-      <c r="G24" s="11" t="n"/>
-    </row>
-    <row r="25">
-      <c r="A25" s="21" t="n">
-        <v>17</v>
-      </c>
-      <c r="B25" s="13" t="inlineStr">
+      <c r="F25" s="30" t="n"/>
+      <c r="G25" s="30" t="n"/>
+    </row>
+    <row r="26">
+      <c r="A26" s="31" t="n">
+        <v>18</v>
+      </c>
+      <c r="B26" s="32" t="inlineStr">
         <is>
           <t>Limpieza extra de cocina (más volumen de lo normal)</t>
         </is>
       </c>
-      <c r="C25" s="14" t="inlineStr">
+      <c r="C26" s="29" t="inlineStr">
         <is>
           <t>Cocina</t>
         </is>
       </c>
-      <c r="D25" s="14" t="inlineStr">
+      <c r="D26" s="29" t="inlineStr">
         <is>
           <t>Auxiliar</t>
         </is>
       </c>
-      <c r="E25" s="14" t="inlineStr">
+      <c r="E26" s="29" t="inlineStr">
         <is>
           <t>15:00</t>
         </is>
       </c>
-      <c r="F25" s="15" t="n"/>
-      <c r="G25" s="15" t="n"/>
-    </row>
-    <row r="26">
-      <c r="A26" s="20" t="n">
-        <v>18</v>
-      </c>
-      <c r="B26" s="9" t="inlineStr">
+      <c r="F26" s="30" t="n"/>
+      <c r="G26" s="30" t="n"/>
+    </row>
+    <row r="27">
+      <c r="A27" s="27" t="n">
+        <v>19</v>
+      </c>
+      <c r="B27" s="28" t="inlineStr">
         <is>
           <t>Anotar qué se vendió más/menos para ajustar semana próxima</t>
         </is>
       </c>
-      <c r="C26" s="10" t="inlineStr">
+      <c r="C27" s="29" t="inlineStr">
         <is>
           <t>Office</t>
         </is>
       </c>
-      <c r="D26" s="10" t="inlineStr">
+      <c r="D27" s="29" t="inlineStr">
         <is>
           <t>Manager</t>
         </is>
       </c>
-      <c r="E26" s="10" t="inlineStr">
+      <c r="E27" s="29" t="inlineStr">
         <is>
           <t>15:00</t>
         </is>
       </c>
-      <c r="F26" s="11" t="n"/>
-      <c r="G26" s="11" t="n"/>
-    </row>
-    <row r="27"/>
+      <c r="F27" s="30" t="n"/>
+      <c r="G27" s="30" t="n"/>
+    </row>
     <row r="28">
-      <c r="C28" s="16" t="inlineStr">
-        <is>
-          <t>Completadas:</t>
-        </is>
-      </c>
-      <c r="D28" s="17">
-        <f>COUNTIF(F5:F26,"✓")</f>
+      <c r="A28" s="33" t="n"/>
+      <c r="B28" s="34" t="n"/>
+      <c r="C28" s="29" t="n"/>
+      <c r="D28" s="29" t="n"/>
+      <c r="E28" s="29" t="n"/>
+      <c r="F28" s="30" t="n"/>
+      <c r="G28" s="30" t="n"/>
+    </row>
+    <row r="29">
+      <c r="A29" s="33" t="n"/>
+      <c r="B29" s="34" t="n"/>
+      <c r="C29" s="29" t="n"/>
+      <c r="D29" s="29" t="n"/>
+      <c r="E29" s="29" t="n"/>
+      <c r="F29" s="30" t="n"/>
+      <c r="G29" s="30" t="n"/>
+    </row>
+    <row r="30">
+      <c r="A30" s="33" t="n"/>
+      <c r="B30" s="34" t="n"/>
+      <c r="C30" s="29" t="n"/>
+      <c r="D30" s="29" t="n"/>
+      <c r="E30" s="29" t="n"/>
+      <c r="F30" s="30" t="n"/>
+      <c r="G30" s="30" t="n"/>
+    </row>
+    <row r="31">
+      <c r="A31" s="33" t="n"/>
+      <c r="B31" s="34" t="n"/>
+      <c r="C31" s="29" t="n"/>
+      <c r="D31" s="29" t="n"/>
+      <c r="E31" s="29" t="n"/>
+      <c r="F31" s="30" t="n"/>
+      <c r="G31" s="30" t="n"/>
+    </row>
+    <row r="32">
+      <c r="A32" s="33" t="n"/>
+      <c r="B32" s="34" t="n"/>
+      <c r="C32" s="29" t="n"/>
+      <c r="D32" s="29" t="n"/>
+      <c r="E32" s="29" t="n"/>
+      <c r="F32" s="30" t="n"/>
+      <c r="G32" s="30" t="n"/>
+    </row>
+    <row r="33"/>
+    <row r="34">
+      <c r="A34" s="16" t="inlineStr">
+        <is>
+          <t>Tareas completadas:</t>
+        </is>
+      </c>
+      <c r="D34" s="17">
+        <f>COUNTIFS(B5:B32,"?*",F5:F32,"✓")</f>
         <v>0.0</v>
       </c>
-      <c r="E28" s="16" t="inlineStr">
+      <c r="E34" s="16" t="inlineStr">
         <is>
           <t>de</t>
         </is>
       </c>
-      <c r="F28">
-        <f>COUNTIF(B5:B26,"?*")</f>
-        <v>18.0</v>
-      </c>
-    </row>
-    <row r="29"/>
-    <row r="30">
-      <c r="A30" s="18" t="inlineStr">
+      <c r="F34">
+        <f>COUNTIF(B5:B32,"?*")-COUNTIF(F5:F32,"N/A")</f>
+        <v>19.0</v>
+      </c>
+    </row>
+    <row r="35"/>
+    <row r="36">
+      <c r="A36" s="18" t="inlineStr">
         <is>
           <t>Firma encargado/a: _________________________    Hora: _________</t>
         </is>
       </c>
     </row>
-    <row r="31"/>
-    <row r="32">
-      <c r="A32" s="19" t="inlineStr">
-        <is>
-          <t>— Kit de Tareas Recurrentes: Cafetería / Brunch · AI Chef Pro · aichef.pro —</t>
+    <row r="37"/>
+    <row r="38">
+      <c r="A38" s="19" t="inlineStr">
+        <is>
+          <t>— Kit de Tareas Recurrentes · Cafetería / Brunch · AI Chef Pro · aichef.pro</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="8">
+  <sheetProtection selectLockedCells="0" selectUnlockedCells="0" sheet="1" objects="0" insertRows="0" insertHyperlinks="1" autoFilter="0" scenarios="0" formatColumns="0" deleteColumns="1" insertColumns="1" pivotTables="1" deleteRows="0" formatCells="0" formatRows="0" sort="0"/>
+  <mergeCells count="9">
+    <mergeCell ref="A36:G36"/>
+    <mergeCell ref="A12:G12"/>
     <mergeCell ref="A1:G1"/>
-    <mergeCell ref="A17:G17"/>
-    <mergeCell ref="A32:G32"/>
     <mergeCell ref="A2:G2"/>
-    <mergeCell ref="A30:G30"/>
-    <mergeCell ref="A23:G23"/>
+    <mergeCell ref="A18:G18"/>
     <mergeCell ref="A5:G5"/>
-    <mergeCell ref="A11:G11"/>
+    <mergeCell ref="A34:C34"/>
+    <mergeCell ref="A24:G24"/>
+    <mergeCell ref="A38:G38"/>
   </mergeCells>
-  <conditionalFormatting sqref="A5:G26">
+  <conditionalFormatting sqref="A5:G32">
     <cfRule type="expression" priority="1" dxfId="0">
       <formula>$F5="✓"</formula>
     </cfRule>
   </conditionalFormatting>
   <dataValidations count="1">
-    <dataValidation sqref="F6 F7 F8 F9 F10 F12 F13 F14 F15 F16 F18 F19 F20 F21 F22 F24 F25 F26" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="F6 F7 F8 F9 F10 F11 F13 F14 F15 F16 F17 F19 F20 F21 F22 F23 F25 F26 F27 F28 F29 F30 F31 F32" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Marca no válida" error="Usa el desplegable: ✓, — o N/A. N/A = no aplica, sale del total; — = no hecha, cuenta como pendiente." type="list" errorStyle="stop">
       <formula1>"✓,—,N/A"</formula1>
     </dataValidation>
   </dataValidations>
@@ -1318,7 +1573,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:G22"/>
+  <dimension ref="A1:G28"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="4" customWidth="1" min="1" max="1"/>
@@ -1340,7 +1595,7 @@
     <row r="2">
       <c r="A2" s="5" t="inlineStr">
         <is>
-          <t>Fecha: ___/___/______    Turno: ☐ Mañana  ☐ Tarde  ☐ Noche    Responsable: ________________</t>
+          <t>Evento / temporada: ___________________    Fecha: ___/___/______    Responsable: _________________________</t>
         </is>
       </c>
     </row>
@@ -1368,7 +1623,7 @@
       </c>
       <c r="E4" s="6" t="inlineStr">
         <is>
-          <t>Hora Límite</t>
+          <t>Antelación</t>
         </is>
       </c>
       <c r="F4" s="6" t="inlineStr">
@@ -1383,342 +1638,428 @@
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="7" t="inlineStr">
+      <c r="A5" s="25" t="inlineStr">
         <is>
           <t xml:space="preserve">  PREPARACIÓN (1 SEMANA ANTES)</t>
         </is>
       </c>
+      <c r="B5" s="26" t="n"/>
+      <c r="C5" s="26" t="n"/>
+      <c r="D5" s="26" t="n"/>
+      <c r="E5" s="26" t="n"/>
+      <c r="F5" s="26" t="n"/>
+      <c r="G5" s="26" t="n"/>
     </row>
     <row r="6">
-      <c r="A6" s="20" t="n">
+      <c r="A6" s="27" t="n">
         <v>1</v>
       </c>
-      <c r="B6" s="9" t="inlineStr">
+      <c r="B6" s="28" t="inlineStr">
         <is>
           <t>Diseñar desayuno/brunch especial de San Valentín</t>
         </is>
       </c>
-      <c r="C6" s="10" t="inlineStr">
+      <c r="C6" s="29" t="inlineStr">
         <is>
           <t>Office</t>
         </is>
       </c>
-      <c r="D6" s="10" t="inlineStr">
+      <c r="D6" s="29" t="inlineStr">
         <is>
           <t>Manager</t>
         </is>
       </c>
-      <c r="E6" s="10" t="inlineStr">
+      <c r="E6" s="29" t="inlineStr">
         <is>
           <t>7 días antes</t>
         </is>
       </c>
-      <c r="F6" s="11" t="n"/>
-      <c r="G6" s="11" t="n"/>
+      <c r="F6" s="30" t="n"/>
+      <c r="G6" s="30" t="n"/>
     </row>
     <row r="7">
-      <c r="A7" s="21" t="n">
+      <c r="A7" s="31" t="n">
         <v>2</v>
       </c>
-      <c r="B7" s="13" t="inlineStr">
+      <c r="B7" s="32" t="inlineStr">
         <is>
           <t>Pedir ingredientes especiales (fresas, chocolate, champagne)</t>
         </is>
       </c>
-      <c r="C7" s="14" t="inlineStr">
+      <c r="C7" s="29" t="inlineStr">
         <is>
           <t>Office</t>
         </is>
       </c>
-      <c r="D7" s="14" t="inlineStr">
+      <c r="D7" s="29" t="inlineStr">
         <is>
           <t>Manager</t>
         </is>
       </c>
-      <c r="E7" s="14" t="inlineStr">
+      <c r="E7" s="29" t="inlineStr">
         <is>
           <t>5 días antes</t>
         </is>
       </c>
-      <c r="F7" s="15" t="n"/>
-      <c r="G7" s="15" t="n"/>
+      <c r="F7" s="30" t="n"/>
+      <c r="G7" s="30" t="n"/>
     </row>
     <row r="8">
-      <c r="A8" s="20" t="n">
+      <c r="A8" s="27" t="n">
         <v>3</v>
       </c>
-      <c r="B8" s="9" t="inlineStr">
+      <c r="B8" s="28" t="inlineStr">
         <is>
           <t>Preparar decoración: flores, velas, corazones</t>
         </is>
       </c>
-      <c r="C8" s="10" t="inlineStr">
+      <c r="C8" s="29" t="inlineStr">
         <is>
           <t>Sala</t>
         </is>
       </c>
-      <c r="D8" s="10" t="inlineStr">
+      <c r="D8" s="29" t="inlineStr">
         <is>
           <t>Camarero/a</t>
         </is>
       </c>
-      <c r="E8" s="10" t="inlineStr">
+      <c r="E8" s="29" t="inlineStr">
         <is>
           <t>2 días antes</t>
         </is>
       </c>
-      <c r="F8" s="11" t="n"/>
-      <c r="G8" s="11" t="n"/>
+      <c r="F8" s="30" t="n"/>
+      <c r="G8" s="30" t="n"/>
     </row>
     <row r="9">
-      <c r="A9" s="21" t="n">
+      <c r="A9" s="31" t="n">
         <v>4</v>
       </c>
-      <c r="B9" s="13" t="inlineStr">
+      <c r="B9" s="32" t="inlineStr">
         <is>
           <t>Publicar oferta en RRSS y aceptar reservas</t>
         </is>
       </c>
-      <c r="C9" s="14" t="inlineStr">
+      <c r="C9" s="29" t="inlineStr">
         <is>
           <t>Office</t>
         </is>
       </c>
-      <c r="D9" s="14" t="inlineStr">
+      <c r="D9" s="29" t="inlineStr">
         <is>
           <t>Manager</t>
         </is>
       </c>
-      <c r="E9" s="14" t="inlineStr">
+      <c r="E9" s="29" t="inlineStr">
         <is>
           <t>7 días antes</t>
         </is>
       </c>
-      <c r="F9" s="15" t="n"/>
-      <c r="G9" s="15" t="n"/>
+      <c r="F9" s="30" t="n"/>
+      <c r="G9" s="30" t="n"/>
     </row>
     <row r="10">
-      <c r="A10" s="7" t="inlineStr">
+      <c r="A10" s="31" t="n">
+        <v>5</v>
+      </c>
+      <c r="B10" s="32" t="inlineStr">
+        <is>
+          <t>Al confirmar cada reserva, recoger POR ESCRITO alérgenos e intolerancias y pasarlos a cocina y a barra (gluten, frutos secos, lactosa, huevo)</t>
+        </is>
+      </c>
+      <c r="C10" s="29" t="inlineStr">
+        <is>
+          <t>Office</t>
+        </is>
+      </c>
+      <c r="D10" s="29" t="inlineStr">
+        <is>
+          <t>Manager</t>
+        </is>
+      </c>
+      <c r="E10" s="29" t="inlineStr">
+        <is>
+          <t>Al confirmar</t>
+        </is>
+      </c>
+      <c r="F10" s="30" t="n"/>
+      <c r="G10" s="30" t="n"/>
+    </row>
+    <row r="11">
+      <c r="A11" s="25" t="inlineStr">
         <is>
           <t xml:space="preserve">  DÍA DE SAN VALENTÍN</t>
         </is>
       </c>
-    </row>
-    <row r="11">
-      <c r="A11" s="21" t="n">
-        <v>5</v>
-      </c>
-      <c r="B11" s="13" t="inlineStr">
+      <c r="B11" s="26" t="n"/>
+      <c r="C11" s="26" t="n"/>
+      <c r="D11" s="26" t="n"/>
+      <c r="E11" s="26" t="n"/>
+      <c r="F11" s="26" t="n"/>
+      <c r="G11" s="26" t="n"/>
+    </row>
+    <row r="12">
+      <c r="A12" s="31" t="n">
+        <v>6</v>
+      </c>
+      <c r="B12" s="32" t="inlineStr">
         <is>
           <t>Montar decoración especial</t>
         </is>
       </c>
-      <c r="C11" s="14" t="inlineStr">
+      <c r="C12" s="29" t="inlineStr">
         <is>
           <t>Sala</t>
         </is>
       </c>
-      <c r="D11" s="14" t="inlineStr">
+      <c r="D12" s="29" t="inlineStr">
         <is>
           <t>Camarero/a</t>
         </is>
       </c>
-      <c r="E11" s="14" t="inlineStr">
+      <c r="E12" s="29" t="inlineStr">
         <is>
           <t>07:00</t>
         </is>
       </c>
-      <c r="F11" s="15" t="n"/>
-      <c r="G11" s="15" t="n"/>
-    </row>
-    <row r="12">
-      <c r="A12" s="20" t="n">
-        <v>6</v>
-      </c>
-      <c r="B12" s="9" t="inlineStr">
+      <c r="F12" s="30" t="n"/>
+      <c r="G12" s="30" t="n"/>
+    </row>
+    <row r="13">
+      <c r="A13" s="27" t="n">
+        <v>7</v>
+      </c>
+      <c r="B13" s="28" t="inlineStr">
         <is>
           <t>Preparar latte art especial (corazón)</t>
         </is>
       </c>
-      <c r="C12" s="10" t="inlineStr">
+      <c r="C13" s="29" t="inlineStr">
         <is>
           <t>Barra</t>
         </is>
       </c>
-      <c r="D12" s="10" t="inlineStr">
+      <c r="D13" s="29" t="inlineStr">
         <is>
           <t>Barista</t>
         </is>
       </c>
-      <c r="E12" s="10" t="inlineStr">
+      <c r="E13" s="29" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="F12" s="11" t="n"/>
-      <c r="G12" s="11" t="n"/>
-    </row>
-    <row r="13">
-      <c r="A13" s="21" t="n">
-        <v>7</v>
-      </c>
-      <c r="B13" s="13" t="inlineStr">
+      <c r="F13" s="30" t="n"/>
+      <c r="G13" s="30" t="n"/>
+    </row>
+    <row r="14">
+      <c r="A14" s="31" t="n">
+        <v>8</v>
+      </c>
+      <c r="B14" s="32" t="inlineStr">
         <is>
           <t>Ofrecer tostada con forma de corazón o plato especial</t>
         </is>
       </c>
-      <c r="C13" s="14" t="inlineStr">
+      <c r="C14" s="29" t="inlineStr">
         <is>
           <t>Cocina</t>
         </is>
       </c>
-      <c r="D13" s="14" t="inlineStr">
+      <c r="D14" s="29" t="inlineStr">
         <is>
           <t>Cocinero</t>
         </is>
       </c>
-      <c r="E13" s="14" t="inlineStr">
+      <c r="E14" s="29" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="F13" s="15" t="n"/>
-      <c r="G13" s="15" t="n"/>
-    </row>
-    <row r="14">
-      <c r="A14" s="20" t="n">
-        <v>8</v>
-      </c>
-      <c r="B14" s="9" t="inlineStr">
+      <c r="F14" s="30" t="n"/>
+      <c r="G14" s="30" t="n"/>
+    </row>
+    <row r="15">
+      <c r="A15" s="27" t="n">
+        <v>9</v>
+      </c>
+      <c r="B15" s="28" t="inlineStr">
         <is>
           <t>Postre especial: brownie con fresas / tarta red velvet</t>
         </is>
       </c>
-      <c r="C14" s="10" t="inlineStr">
+      <c r="C15" s="29" t="inlineStr">
         <is>
           <t>Cocina</t>
         </is>
       </c>
-      <c r="D14" s="10" t="inlineStr">
+      <c r="D15" s="29" t="inlineStr">
         <is>
           <t>Pastelero/a</t>
         </is>
       </c>
-      <c r="E14" s="10" t="inlineStr">
+      <c r="E15" s="29" t="inlineStr">
         <is>
           <t>06:30</t>
         </is>
       </c>
-      <c r="F14" s="11" t="n"/>
-      <c r="G14" s="11" t="n"/>
-    </row>
-    <row r="15">
-      <c r="A15" s="21" t="n">
-        <v>9</v>
-      </c>
-      <c r="B15" s="13" t="inlineStr">
+      <c r="F15" s="30" t="n"/>
+      <c r="G15" s="30" t="n"/>
+    </row>
+    <row r="16">
+      <c r="A16" s="31" t="n">
+        <v>10</v>
+      </c>
+      <c r="B16" s="32" t="inlineStr">
         <is>
           <t>Mimosa de cortesía para parejas (si aplica)</t>
         </is>
       </c>
-      <c r="C15" s="14" t="inlineStr">
+      <c r="C16" s="29" t="inlineStr">
         <is>
           <t>Barra</t>
         </is>
       </c>
-      <c r="D15" s="14" t="inlineStr">
+      <c r="D16" s="29" t="inlineStr">
         <is>
           <t>Barista</t>
         </is>
       </c>
-      <c r="E15" s="14" t="inlineStr">
+      <c r="E16" s="29" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="F15" s="15" t="n"/>
-      <c r="G15" s="15" t="n"/>
-    </row>
-    <row r="16">
-      <c r="A16" s="20" t="n">
-        <v>10</v>
-      </c>
-      <c r="B16" s="9" t="inlineStr">
+      <c r="F16" s="30" t="n"/>
+      <c r="G16" s="30" t="n"/>
+    </row>
+    <row r="17">
+      <c r="A17" s="27" t="n">
+        <v>11</v>
+      </c>
+      <c r="B17" s="28" t="inlineStr">
         <is>
           <t>Hacer fotos para RRSS durante el servicio</t>
         </is>
       </c>
-      <c r="C16" s="10" t="inlineStr">
+      <c r="C17" s="29" t="inlineStr">
         <is>
           <t>General</t>
         </is>
       </c>
-      <c r="D16" s="10" t="inlineStr">
+      <c r="D17" s="29" t="inlineStr">
         <is>
           <t>Manager</t>
         </is>
       </c>
-      <c r="E16" s="10" t="inlineStr">
+      <c r="E17" s="29" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="F16" s="11" t="n"/>
-      <c r="G16" s="11" t="n"/>
-    </row>
-    <row r="17"/>
+      <c r="F17" s="30" t="n"/>
+      <c r="G17" s="30" t="n"/>
+    </row>
     <row r="18">
-      <c r="C18" s="16" t="inlineStr">
-        <is>
-          <t>Completadas:</t>
-        </is>
-      </c>
-      <c r="D18" s="17">
-        <f>COUNTIF(F5:F16,"✓")</f>
+      <c r="A18" s="33" t="n"/>
+      <c r="B18" s="34" t="n"/>
+      <c r="C18" s="29" t="n"/>
+      <c r="D18" s="29" t="n"/>
+      <c r="E18" s="29" t="n"/>
+      <c r="F18" s="30" t="n"/>
+      <c r="G18" s="30" t="n"/>
+    </row>
+    <row r="19">
+      <c r="A19" s="33" t="n"/>
+      <c r="B19" s="34" t="n"/>
+      <c r="C19" s="29" t="n"/>
+      <c r="D19" s="29" t="n"/>
+      <c r="E19" s="29" t="n"/>
+      <c r="F19" s="30" t="n"/>
+      <c r="G19" s="30" t="n"/>
+    </row>
+    <row r="20">
+      <c r="A20" s="33" t="n"/>
+      <c r="B20" s="34" t="n"/>
+      <c r="C20" s="29" t="n"/>
+      <c r="D20" s="29" t="n"/>
+      <c r="E20" s="29" t="n"/>
+      <c r="F20" s="30" t="n"/>
+      <c r="G20" s="30" t="n"/>
+    </row>
+    <row r="21">
+      <c r="A21" s="33" t="n"/>
+      <c r="B21" s="34" t="n"/>
+      <c r="C21" s="29" t="n"/>
+      <c r="D21" s="29" t="n"/>
+      <c r="E21" s="29" t="n"/>
+      <c r="F21" s="30" t="n"/>
+      <c r="G21" s="30" t="n"/>
+    </row>
+    <row r="22">
+      <c r="A22" s="33" t="n"/>
+      <c r="B22" s="34" t="n"/>
+      <c r="C22" s="29" t="n"/>
+      <c r="D22" s="29" t="n"/>
+      <c r="E22" s="29" t="n"/>
+      <c r="F22" s="30" t="n"/>
+      <c r="G22" s="30" t="n"/>
+    </row>
+    <row r="23"/>
+    <row r="24">
+      <c r="A24" s="16" t="inlineStr">
+        <is>
+          <t>Tareas completadas:</t>
+        </is>
+      </c>
+      <c r="D24" s="17">
+        <f>COUNTIFS(B5:B22,"?*",F5:F22,"✓")</f>
         <v>0.0</v>
       </c>
-      <c r="E18" s="16" t="inlineStr">
+      <c r="E24" s="16" t="inlineStr">
         <is>
           <t>de</t>
         </is>
       </c>
-      <c r="F18">
-        <f>COUNTIF(B5:B16,"?*")</f>
-        <v>10.0</v>
-      </c>
-    </row>
-    <row r="19"/>
-    <row r="20">
-      <c r="A20" s="18" t="inlineStr">
+      <c r="F24">
+        <f>COUNTIF(B5:B22,"?*")-COUNTIF(F5:F22,"N/A")</f>
+        <v>11.0</v>
+      </c>
+    </row>
+    <row r="25"/>
+    <row r="26">
+      <c r="A26" s="18" t="inlineStr">
         <is>
           <t>Firma encargado/a: _________________________    Hora: _________</t>
         </is>
       </c>
     </row>
-    <row r="21"/>
-    <row r="22">
-      <c r="A22" s="19" t="inlineStr">
-        <is>
-          <t>— Kit de Tareas Recurrentes: Cafetería / Brunch · AI Chef Pro · aichef.pro —</t>
+    <row r="27"/>
+    <row r="28">
+      <c r="A28" s="19" t="inlineStr">
+        <is>
+          <t>— Kit de Tareas Recurrentes · Cafetería / Brunch · AI Chef Pro · aichef.pro</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="6">
-    <mergeCell ref="A20:G20"/>
+  <sheetProtection selectLockedCells="0" selectUnlockedCells="0" sheet="1" objects="0" insertRows="0" insertHyperlinks="1" autoFilter="0" scenarios="0" formatColumns="0" deleteColumns="1" insertColumns="1" pivotTables="1" deleteRows="0" formatCells="0" formatRows="0" sort="0"/>
+  <mergeCells count="7">
+    <mergeCell ref="A28:G28"/>
     <mergeCell ref="A1:G1"/>
     <mergeCell ref="A2:G2"/>
-    <mergeCell ref="A22:G22"/>
+    <mergeCell ref="A11:G11"/>
+    <mergeCell ref="A24:C24"/>
     <mergeCell ref="A5:G5"/>
-    <mergeCell ref="A10:G10"/>
+    <mergeCell ref="A26:G26"/>
   </mergeCells>
-  <conditionalFormatting sqref="A5:G16">
+  <conditionalFormatting sqref="A5:G22">
     <cfRule type="expression" priority="1" dxfId="0">
       <formula>$F5="✓"</formula>
     </cfRule>
   </conditionalFormatting>
   <dataValidations count="1">
-    <dataValidation sqref="F6 F7 F8 F9 F11 F12 F13 F14 F15 F16" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="F6 F7 F8 F9 F10 F12 F13 F14 F15 F16 F17 F18 F19 F20 F21 F22" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Marca no válida" error="Usa el desplegable: ✓, — o N/A. N/A = no aplica, sale del total; — = no hecha, cuenta como pendiente." type="list" errorStyle="stop">
       <formula1>"✓,—,N/A"</formula1>
     </dataValidation>
   </dataValidations>
@@ -1742,7 +2083,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:G29"/>
+  <dimension ref="A1:G34"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="4" customWidth="1" min="1" max="1"/>
@@ -1792,7 +2133,7 @@
       </c>
       <c r="E4" s="6" t="inlineStr">
         <is>
-          <t>Hora Límite</t>
+          <t>Cuándo</t>
         </is>
       </c>
       <c r="F4" s="6" t="inlineStr">
@@ -1807,493 +2148,564 @@
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="7" t="inlineStr">
+      <c r="A5" s="25" t="inlineStr">
         <is>
           <t xml:space="preserve">  PREPARACIÓN (2 SEMANAS ANTES)</t>
         </is>
       </c>
+      <c r="B5" s="26" t="n"/>
+      <c r="C5" s="26" t="n"/>
+      <c r="D5" s="26" t="n"/>
+      <c r="E5" s="26" t="n"/>
+      <c r="F5" s="26" t="n"/>
+      <c r="G5" s="26" t="n"/>
     </row>
     <row r="6">
-      <c r="A6" s="20" t="n">
+      <c r="A6" s="27" t="n">
         <v>1</v>
       </c>
-      <c r="B6" s="9" t="inlineStr">
+      <c r="B6" s="28" t="inlineStr">
         <is>
           <t>Diseñar carta navideña especial</t>
         </is>
       </c>
-      <c r="C6" s="10" t="inlineStr">
+      <c r="C6" s="29" t="inlineStr">
         <is>
           <t>Office</t>
         </is>
       </c>
-      <c r="D6" s="10" t="inlineStr">
+      <c r="D6" s="29" t="inlineStr">
         <is>
           <t>Manager</t>
         </is>
       </c>
-      <c r="E6" s="10" t="inlineStr">
+      <c r="E6" s="29" t="inlineStr">
         <is>
           <t>15 días antes</t>
         </is>
       </c>
-      <c r="F6" s="11" t="n"/>
-      <c r="G6" s="11" t="n"/>
+      <c r="F6" s="30" t="n"/>
+      <c r="G6" s="30" t="n"/>
     </row>
     <row r="7">
-      <c r="A7" s="21" t="n">
+      <c r="A7" s="31" t="n">
         <v>2</v>
       </c>
-      <c r="B7" s="13" t="inlineStr">
+      <c r="B7" s="32" t="inlineStr">
         <is>
           <t>Pedir stock: panettone, turrón, cava, chocolate caliente especial</t>
         </is>
       </c>
-      <c r="C7" s="14" t="inlineStr">
+      <c r="C7" s="29" t="inlineStr">
         <is>
           <t>Office</t>
         </is>
       </c>
-      <c r="D7" s="14" t="inlineStr">
+      <c r="D7" s="29" t="inlineStr">
         <is>
           <t>Manager</t>
         </is>
       </c>
-      <c r="E7" s="14" t="inlineStr">
+      <c r="E7" s="29" t="inlineStr">
         <is>
           <t>10 días antes</t>
         </is>
       </c>
-      <c r="F7" s="15" t="n"/>
-      <c r="G7" s="15" t="n"/>
+      <c r="F7" s="30" t="n"/>
+      <c r="G7" s="30" t="n"/>
     </row>
     <row r="8">
-      <c r="A8" s="20" t="n">
+      <c r="A8" s="27" t="n">
         <v>3</v>
       </c>
-      <c r="B8" s="9" t="inlineStr">
+      <c r="B8" s="28" t="inlineStr">
         <is>
           <t>Comprar decoración navideña</t>
         </is>
       </c>
-      <c r="C8" s="10" t="inlineStr">
+      <c r="C8" s="29" t="inlineStr">
         <is>
           <t>Office</t>
         </is>
       </c>
-      <c r="D8" s="10" t="inlineStr">
+      <c r="D8" s="29" t="inlineStr">
         <is>
           <t>Manager</t>
         </is>
       </c>
-      <c r="E8" s="10" t="inlineStr">
+      <c r="E8" s="29" t="inlineStr">
         <is>
           <t>15 días antes</t>
         </is>
       </c>
-      <c r="F8" s="11" t="n"/>
-      <c r="G8" s="11" t="n"/>
+      <c r="F8" s="30" t="n"/>
+      <c r="G8" s="30" t="n"/>
     </row>
     <row r="9">
-      <c r="A9" s="21" t="n">
+      <c r="A9" s="31" t="n">
         <v>4</v>
       </c>
-      <c r="B9" s="13" t="inlineStr">
+      <c r="B9" s="32" t="inlineStr">
         <is>
           <t>Planificar horarios especiales (Nochebuena, Navidad, Año Nuevo)</t>
         </is>
       </c>
-      <c r="C9" s="14" t="inlineStr">
+      <c r="C9" s="29" t="inlineStr">
         <is>
           <t>Office</t>
         </is>
       </c>
-      <c r="D9" s="14" t="inlineStr">
+      <c r="D9" s="29" t="inlineStr">
         <is>
           <t>Manager</t>
         </is>
       </c>
-      <c r="E9" s="14" t="inlineStr">
+      <c r="E9" s="29" t="inlineStr">
         <is>
           <t>10 días antes</t>
         </is>
       </c>
-      <c r="F9" s="15" t="n"/>
-      <c r="G9" s="15" t="n"/>
+      <c r="F9" s="30" t="n"/>
+      <c r="G9" s="30" t="n"/>
     </row>
     <row r="10">
-      <c r="A10" s="7" t="inlineStr">
+      <c r="A10" s="25" t="inlineStr">
         <is>
           <t xml:space="preserve">  MONTAJE NAVIDEÑO</t>
         </is>
       </c>
+      <c r="B10" s="26" t="n"/>
+      <c r="C10" s="26" t="n"/>
+      <c r="D10" s="26" t="n"/>
+      <c r="E10" s="26" t="n"/>
+      <c r="F10" s="26" t="n"/>
+      <c r="G10" s="26" t="n"/>
     </row>
     <row r="11">
-      <c r="A11" s="21" t="n">
+      <c r="A11" s="31" t="n">
         <v>5</v>
       </c>
-      <c r="B11" s="13" t="inlineStr">
+      <c r="B11" s="32" t="inlineStr">
         <is>
           <t>Decorar local: luces, guirnaldas, árbol si aplica</t>
         </is>
       </c>
-      <c r="C11" s="14" t="inlineStr">
+      <c r="C11" s="29" t="inlineStr">
         <is>
           <t>Sala</t>
         </is>
       </c>
-      <c r="D11" s="14" t="inlineStr">
+      <c r="D11" s="29" t="inlineStr">
         <is>
           <t>Camarero/a</t>
         </is>
       </c>
-      <c r="E11" s="14" t="inlineStr">
+      <c r="E11" s="29" t="inlineStr">
         <is>
           <t>Dic 1</t>
         </is>
       </c>
-      <c r="F11" s="15" t="n"/>
-      <c r="G11" s="15" t="n"/>
+      <c r="F11" s="30" t="n"/>
+      <c r="G11" s="30" t="n"/>
     </row>
     <row r="12">
-      <c r="A12" s="20" t="n">
+      <c r="A12" s="27" t="n">
         <v>6</v>
       </c>
-      <c r="B12" s="9" t="inlineStr">
+      <c r="B12" s="28" t="inlineStr">
         <is>
           <t>Decorar vitrina con tema navideño</t>
         </is>
       </c>
-      <c r="C12" s="10" t="inlineStr">
+      <c r="C12" s="29" t="inlineStr">
         <is>
           <t>Barra</t>
         </is>
       </c>
-      <c r="D12" s="10" t="inlineStr">
+      <c r="D12" s="29" t="inlineStr">
         <is>
           <t>Pastelero/a</t>
         </is>
       </c>
-      <c r="E12" s="10" t="inlineStr">
+      <c r="E12" s="29" t="inlineStr">
         <is>
           <t>Dic 1</t>
         </is>
       </c>
-      <c r="F12" s="11" t="n"/>
-      <c r="G12" s="11" t="n"/>
+      <c r="F12" s="30" t="n"/>
+      <c r="G12" s="30" t="n"/>
     </row>
     <row r="13">
-      <c r="A13" s="21" t="n">
+      <c r="A13" s="31" t="n">
         <v>7</v>
       </c>
-      <c r="B13" s="13" t="inlineStr">
+      <c r="B13" s="32" t="inlineStr">
         <is>
           <t>Actualizar pizarra con carta de Navidad</t>
         </is>
       </c>
-      <c r="C13" s="14" t="inlineStr">
+      <c r="C13" s="29" t="inlineStr">
         <is>
           <t>Sala</t>
         </is>
       </c>
-      <c r="D13" s="14" t="inlineStr">
+      <c r="D13" s="29" t="inlineStr">
         <is>
           <t>Manager</t>
         </is>
       </c>
-      <c r="E13" s="14" t="inlineStr">
+      <c r="E13" s="29" t="inlineStr">
         <is>
           <t>Dic 1</t>
         </is>
       </c>
-      <c r="F13" s="15" t="n"/>
-      <c r="G13" s="15" t="n"/>
+      <c r="F13" s="30" t="n"/>
+      <c r="G13" s="30" t="n"/>
     </row>
     <row r="14">
-      <c r="A14" s="7" t="inlineStr">
+      <c r="A14" s="25" t="inlineStr">
         <is>
           <t xml:space="preserve">  SERVICIO NAVIDEÑO</t>
         </is>
       </c>
+      <c r="B14" s="26" t="n"/>
+      <c r="C14" s="26" t="n"/>
+      <c r="D14" s="26" t="n"/>
+      <c r="E14" s="26" t="n"/>
+      <c r="F14" s="26" t="n"/>
+      <c r="G14" s="26" t="n"/>
     </row>
     <row r="15">
-      <c r="A15" s="21" t="n">
+      <c r="A15" s="31" t="n">
         <v>8</v>
       </c>
-      <c r="B15" s="13" t="inlineStr">
+      <c r="B15" s="32" t="inlineStr">
         <is>
           <t>Café especial navideño: gingerbread latte, pumpkin spice</t>
         </is>
       </c>
-      <c r="C15" s="14" t="inlineStr">
+      <c r="C15" s="29" t="inlineStr">
         <is>
           <t>Barra</t>
         </is>
       </c>
-      <c r="D15" s="14" t="inlineStr">
+      <c r="D15" s="29" t="inlineStr">
         <is>
           <t>Barista</t>
         </is>
       </c>
-      <c r="E15" s="14" t="inlineStr">
+      <c r="E15" s="29" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="F15" s="15" t="n"/>
-      <c r="G15" s="15" t="n"/>
+      <c r="F15" s="30" t="n"/>
+      <c r="G15" s="30" t="n"/>
     </row>
     <row r="16">
-      <c r="A16" s="20" t="n">
+      <c r="A16" s="27" t="n">
         <v>9</v>
       </c>
-      <c r="B16" s="9" t="inlineStr">
+      <c r="B16" s="28" t="inlineStr">
         <is>
           <t>Chocolate caliente especial con toppings navideños</t>
         </is>
       </c>
-      <c r="C16" s="10" t="inlineStr">
+      <c r="C16" s="29" t="inlineStr">
         <is>
           <t>Barra</t>
         </is>
       </c>
-      <c r="D16" s="10" t="inlineStr">
+      <c r="D16" s="29" t="inlineStr">
         <is>
           <t>Barista</t>
         </is>
       </c>
-      <c r="E16" s="10" t="inlineStr">
+      <c r="E16" s="29" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="F16" s="11" t="n"/>
-      <c r="G16" s="11" t="n"/>
+      <c r="F16" s="30" t="n"/>
+      <c r="G16" s="30" t="n"/>
     </row>
     <row r="17">
-      <c r="A17" s="21" t="n">
+      <c r="A17" s="31" t="n">
         <v>10</v>
       </c>
-      <c r="B17" s="13" t="inlineStr">
+      <c r="B17" s="32" t="inlineStr">
         <is>
           <t>Bollería navideña: panettone, roscón, stollen</t>
         </is>
       </c>
-      <c r="C17" s="14" t="inlineStr">
+      <c r="C17" s="29" t="inlineStr">
         <is>
           <t>Cocina</t>
         </is>
       </c>
-      <c r="D17" s="14" t="inlineStr">
+      <c r="D17" s="29" t="inlineStr">
         <is>
           <t>Pastelero/a</t>
         </is>
       </c>
-      <c r="E17" s="14" t="inlineStr">
+      <c r="E17" s="29" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="F17" s="15" t="n"/>
-      <c r="G17" s="15" t="n"/>
+      <c r="F17" s="30" t="n"/>
+      <c r="G17" s="30" t="n"/>
     </row>
     <row r="18">
-      <c r="A18" s="20" t="n">
+      <c r="A18" s="27" t="n">
         <v>11</v>
       </c>
-      <c r="B18" s="9" t="inlineStr">
+      <c r="B18" s="28" t="inlineStr">
         <is>
           <t>Ofrecer turrón o polvorón con el café</t>
         </is>
       </c>
-      <c r="C18" s="10" t="inlineStr">
+      <c r="C18" s="29" t="inlineStr">
         <is>
           <t>Sala</t>
         </is>
       </c>
-      <c r="D18" s="10" t="inlineStr">
+      <c r="D18" s="29" t="inlineStr">
         <is>
           <t>Camarero/a</t>
         </is>
       </c>
-      <c r="E18" s="10" t="inlineStr">
+      <c r="E18" s="29" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="F18" s="11" t="n"/>
-      <c r="G18" s="11" t="n"/>
+      <c r="F18" s="30" t="n"/>
+      <c r="G18" s="30" t="n"/>
     </row>
     <row r="19">
-      <c r="A19" s="21" t="n">
+      <c r="A19" s="31" t="n">
         <v>12</v>
       </c>
-      <c r="B19" s="13" t="inlineStr">
+      <c r="B19" s="32" t="inlineStr">
         <is>
           <t>Hacer fotos navideñas para RRSS</t>
         </is>
       </c>
-      <c r="C19" s="14" t="inlineStr">
+      <c r="C19" s="29" t="inlineStr">
         <is>
           <t>General</t>
         </is>
       </c>
-      <c r="D19" s="14" t="inlineStr">
+      <c r="D19" s="29" t="inlineStr">
         <is>
           <t>Manager</t>
         </is>
       </c>
-      <c r="E19" s="14" t="inlineStr">
+      <c r="E19" s="29" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="F19" s="15" t="n"/>
-      <c r="G19" s="15" t="n"/>
+      <c r="F19" s="30" t="n"/>
+      <c r="G19" s="30" t="n"/>
     </row>
     <row r="20">
-      <c r="A20" s="7" t="inlineStr">
+      <c r="A20" s="25" t="inlineStr">
         <is>
           <t xml:space="preserve">  CIERRE DE AÑO</t>
         </is>
       </c>
+      <c r="B20" s="26" t="n"/>
+      <c r="C20" s="26" t="n"/>
+      <c r="D20" s="26" t="n"/>
+      <c r="E20" s="26" t="n"/>
+      <c r="F20" s="26" t="n"/>
+      <c r="G20" s="26" t="n"/>
     </row>
     <row r="21">
-      <c r="A21" s="21" t="n">
+      <c r="A21" s="31" t="n">
         <v>13</v>
       </c>
-      <c r="B21" s="13" t="inlineStr">
+      <c r="B21" s="32" t="inlineStr">
         <is>
           <t>Verificar stock para semana sin entregas</t>
         </is>
       </c>
-      <c r="C21" s="14" t="inlineStr">
+      <c r="C21" s="29" t="inlineStr">
         <is>
           <t>Almacén</t>
         </is>
       </c>
-      <c r="D21" s="14" t="inlineStr">
+      <c r="D21" s="29" t="inlineStr">
         <is>
           <t>Manager</t>
         </is>
       </c>
-      <c r="E21" s="14" t="inlineStr">
+      <c r="E21" s="29" t="inlineStr">
         <is>
           <t>23 Dic</t>
         </is>
       </c>
-      <c r="F21" s="15" t="n"/>
-      <c r="G21" s="15" t="n"/>
+      <c r="F21" s="30" t="n"/>
+      <c r="G21" s="30" t="n"/>
     </row>
     <row r="22">
-      <c r="A22" s="20" t="n">
+      <c r="A22" s="27" t="n">
         <v>14</v>
       </c>
-      <c r="B22" s="9" t="inlineStr">
+      <c r="B22" s="28" t="inlineStr">
         <is>
           <t>Planificar equipo mínimo para festivos</t>
         </is>
       </c>
-      <c r="C22" s="10" t="inlineStr">
+      <c r="C22" s="29" t="inlineStr">
         <is>
           <t>Office</t>
         </is>
       </c>
-      <c r="D22" s="10" t="inlineStr">
+      <c r="D22" s="29" t="inlineStr">
         <is>
           <t>Manager</t>
         </is>
       </c>
-      <c r="E22" s="10" t="inlineStr">
+      <c r="E22" s="29" t="inlineStr">
         <is>
           <t>20 Dic</t>
         </is>
       </c>
-      <c r="F22" s="11" t="n"/>
-      <c r="G22" s="11" t="n"/>
+      <c r="F22" s="30" t="n"/>
+      <c r="G22" s="30" t="n"/>
     </row>
     <row r="23">
-      <c r="A23" s="21" t="n">
+      <c r="A23" s="31" t="n">
         <v>15</v>
       </c>
-      <c r="B23" s="13" t="inlineStr">
+      <c r="B23" s="32" t="inlineStr">
         <is>
           <t>Retirar decoración navideña después de Reyes</t>
         </is>
       </c>
-      <c r="C23" s="14" t="inlineStr">
+      <c r="C23" s="29" t="inlineStr">
         <is>
           <t>Sala</t>
         </is>
       </c>
-      <c r="D23" s="14" t="inlineStr">
+      <c r="D23" s="29" t="inlineStr">
         <is>
           <t>Camarero/a</t>
         </is>
       </c>
-      <c r="E23" s="14" t="inlineStr">
+      <c r="E23" s="29" t="inlineStr">
         <is>
           <t>7 Ene</t>
         </is>
       </c>
-      <c r="F23" s="15" t="n"/>
-      <c r="G23" s="15" t="n"/>
-    </row>
-    <row r="24"/>
+      <c r="F23" s="30" t="n"/>
+      <c r="G23" s="30" t="n"/>
+    </row>
+    <row r="24">
+      <c r="A24" s="33" t="n"/>
+      <c r="B24" s="34" t="n"/>
+      <c r="C24" s="29" t="n"/>
+      <c r="D24" s="29" t="n"/>
+      <c r="E24" s="29" t="n"/>
+      <c r="F24" s="30" t="n"/>
+      <c r="G24" s="30" t="n"/>
+    </row>
     <row r="25">
-      <c r="C25" s="16" t="inlineStr">
-        <is>
-          <t>Completadas:</t>
-        </is>
-      </c>
-      <c r="D25" s="17">
-        <f>COUNTIF(F5:F23,"✓")</f>
+      <c r="A25" s="33" t="n"/>
+      <c r="B25" s="34" t="n"/>
+      <c r="C25" s="29" t="n"/>
+      <c r="D25" s="29" t="n"/>
+      <c r="E25" s="29" t="n"/>
+      <c r="F25" s="30" t="n"/>
+      <c r="G25" s="30" t="n"/>
+    </row>
+    <row r="26">
+      <c r="A26" s="33" t="n"/>
+      <c r="B26" s="34" t="n"/>
+      <c r="C26" s="29" t="n"/>
+      <c r="D26" s="29" t="n"/>
+      <c r="E26" s="29" t="n"/>
+      <c r="F26" s="30" t="n"/>
+      <c r="G26" s="30" t="n"/>
+    </row>
+    <row r="27">
+      <c r="A27" s="33" t="n"/>
+      <c r="B27" s="34" t="n"/>
+      <c r="C27" s="29" t="n"/>
+      <c r="D27" s="29" t="n"/>
+      <c r="E27" s="29" t="n"/>
+      <c r="F27" s="30" t="n"/>
+      <c r="G27" s="30" t="n"/>
+    </row>
+    <row r="28">
+      <c r="A28" s="33" t="n"/>
+      <c r="B28" s="34" t="n"/>
+      <c r="C28" s="29" t="n"/>
+      <c r="D28" s="29" t="n"/>
+      <c r="E28" s="29" t="n"/>
+      <c r="F28" s="30" t="n"/>
+      <c r="G28" s="30" t="n"/>
+    </row>
+    <row r="29"/>
+    <row r="30">
+      <c r="A30" s="16" t="inlineStr">
+        <is>
+          <t>Tareas completadas:</t>
+        </is>
+      </c>
+      <c r="D30" s="17">
+        <f>COUNTIFS(B5:B28,"?*",F5:F28,"✓")</f>
         <v>0.0</v>
       </c>
-      <c r="E25" s="16" t="inlineStr">
+      <c r="E30" s="16" t="inlineStr">
         <is>
           <t>de</t>
         </is>
       </c>
-      <c r="F25">
-        <f>COUNTIF(B5:B23,"?*")</f>
+      <c r="F30">
+        <f>COUNTIF(B5:B28,"?*")-COUNTIF(F5:F28,"N/A")</f>
         <v>15.0</v>
       </c>
     </row>
-    <row r="26"/>
-    <row r="27">
-      <c r="A27" s="18" t="inlineStr">
+    <row r="31"/>
+    <row r="32">
+      <c r="A32" s="18" t="inlineStr">
         <is>
           <t>Firma encargado/a: _________________________    Hora: _________</t>
         </is>
       </c>
     </row>
-    <row r="28"/>
-    <row r="29">
-      <c r="A29" s="19" t="inlineStr">
-        <is>
-          <t>— Kit de Tareas Recurrentes: Cafetería / Brunch · AI Chef Pro · aichef.pro —</t>
+    <row r="33"/>
+    <row r="34">
+      <c r="A34" s="19" t="inlineStr">
+        <is>
+          <t>— Kit de Tareas Recurrentes · Cafetería / Brunch · AI Chef Pro · aichef.pro</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="8">
+  <sheetProtection selectLockedCells="0" selectUnlockedCells="0" sheet="1" objects="0" insertRows="0" insertHyperlinks="1" autoFilter="0" scenarios="0" formatColumns="0" deleteColumns="1" insertColumns="1" pivotTables="1" deleteRows="0" formatCells="0" formatRows="0" sort="0"/>
+  <mergeCells count="9">
     <mergeCell ref="A20:G20"/>
     <mergeCell ref="A1:G1"/>
-    <mergeCell ref="A27:G27"/>
+    <mergeCell ref="A32:G32"/>
+    <mergeCell ref="A14:G14"/>
     <mergeCell ref="A2:G2"/>
-    <mergeCell ref="A14:G14"/>
+    <mergeCell ref="A34:G34"/>
+    <mergeCell ref="A30:C30"/>
     <mergeCell ref="A5:G5"/>
-    <mergeCell ref="A29:G29"/>
     <mergeCell ref="A10:G10"/>
   </mergeCells>
-  <conditionalFormatting sqref="A5:G23">
+  <conditionalFormatting sqref="A5:G28">
     <cfRule type="expression" priority="1" dxfId="0">
       <formula>$F5="✓"</formula>
     </cfRule>
   </conditionalFormatting>
   <dataValidations count="1">
-    <dataValidation sqref="F6 F7 F8 F9 F11 F12 F13 F15 F16 F17 F18 F19 F21 F22 F23" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="F6 F7 F8 F9 F11 F12 F13 F15 F16 F17 F18 F19 F21 F22 F23 F24 F25 F26 F27 F28" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Marca no válida" error="Usa el desplegable: ✓, — o N/A. N/A = no aplica, sale del total; — = no hecha, cuenta como pendiente." type="list" errorStyle="stop">
       <formula1>"✓,—,N/A"</formula1>
     </dataValidation>
   </dataValidations>
@@ -2317,7 +2729,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:G24"/>
+  <dimension ref="A1:G29"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="4" customWidth="1" min="1" max="1"/>
@@ -2367,7 +2779,7 @@
       </c>
       <c r="E4" s="6" t="inlineStr">
         <is>
-          <t>Hora Límite</t>
+          <t>Cuándo</t>
         </is>
       </c>
       <c r="F4" s="6" t="inlineStr">
@@ -2382,396 +2794,455 @@
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="7" t="inlineStr">
+      <c r="A5" s="25" t="inlineStr">
         <is>
           <t xml:space="preserve">  APERTURA DE TERRAZA (PRIMAVERA)</t>
         </is>
       </c>
+      <c r="B5" s="26" t="n"/>
+      <c r="C5" s="26" t="n"/>
+      <c r="D5" s="26" t="n"/>
+      <c r="E5" s="26" t="n"/>
+      <c r="F5" s="26" t="n"/>
+      <c r="G5" s="26" t="n"/>
     </row>
     <row r="6">
-      <c r="A6" s="20" t="n">
+      <c r="A6" s="27" t="n">
         <v>1</v>
       </c>
-      <c r="B6" s="9" t="inlineStr">
+      <c r="B6" s="28" t="inlineStr">
+        <is>
+          <t>Verificar el permiso/licencia de terraza vigente y renovarlo si caduca esta temporada</t>
+        </is>
+      </c>
+      <c r="C6" s="29" t="inlineStr">
+        <is>
+          <t>Office</t>
+        </is>
+      </c>
+      <c r="D6" s="29" t="inlineStr">
+        <is>
+          <t>Manager</t>
+        </is>
+      </c>
+      <c r="E6" s="29" t="inlineStr">
+        <is>
+          <t>1 mes antes</t>
+        </is>
+      </c>
+      <c r="F6" s="30" t="n"/>
+      <c r="G6" s="30" t="n"/>
+    </row>
+    <row r="7">
+      <c r="A7" s="31" t="n">
+        <v>2</v>
+      </c>
+      <c r="B7" s="32" t="inlineStr">
         <is>
           <t>Sacar mobiliario de almacén / desembalar</t>
         </is>
       </c>
-      <c r="C6" s="10" t="inlineStr">
+      <c r="C7" s="29" t="inlineStr">
         <is>
           <t>Terraza</t>
         </is>
       </c>
-      <c r="D6" s="10" t="inlineStr">
+      <c r="D7" s="29" t="inlineStr">
         <is>
           <t>Auxiliar</t>
         </is>
       </c>
-      <c r="E6" s="10" t="inlineStr">
+      <c r="E7" s="29" t="inlineStr">
         <is>
           <t>Primavera</t>
         </is>
       </c>
-      <c r="F6" s="11" t="n"/>
-      <c r="G6" s="11" t="n"/>
-    </row>
-    <row r="7">
-      <c r="A7" s="21" t="n">
-        <v>2</v>
-      </c>
-      <c r="B7" s="13" t="inlineStr">
+      <c r="F7" s="30" t="n"/>
+      <c r="G7" s="30" t="n"/>
+    </row>
+    <row r="8">
+      <c r="A8" s="27" t="n">
+        <v>3</v>
+      </c>
+      <c r="B8" s="28" t="inlineStr">
+        <is>
+          <t>Verificar estado: tornillos, estabilidad, pintura</t>
+        </is>
+      </c>
+      <c r="C8" s="29" t="inlineStr">
+        <is>
+          <t>Terraza</t>
+        </is>
+      </c>
+      <c r="D8" s="29" t="inlineStr">
+        <is>
+          <t>Manager</t>
+        </is>
+      </c>
+      <c r="E8" s="29" t="inlineStr">
+        <is>
+          <t>Primavera</t>
+        </is>
+      </c>
+      <c r="F8" s="30" t="n"/>
+      <c r="G8" s="30" t="n"/>
+    </row>
+    <row r="9">
+      <c r="A9" s="31" t="n">
+        <v>4</v>
+      </c>
+      <c r="B9" s="32" t="inlineStr">
         <is>
           <t>Limpiar todas las mesas y sillas a fondo</t>
         </is>
       </c>
-      <c r="C7" s="14" t="inlineStr">
+      <c r="C9" s="29" t="inlineStr">
         <is>
           <t>Terraza</t>
         </is>
       </c>
-      <c r="D7" s="14" t="inlineStr">
+      <c r="D9" s="29" t="inlineStr">
         <is>
           <t>Auxiliar</t>
         </is>
       </c>
-      <c r="E7" s="14" t="inlineStr">
+      <c r="E9" s="29" t="inlineStr">
         <is>
           <t>Primavera</t>
         </is>
       </c>
-      <c r="F7" s="15" t="n"/>
-      <c r="G7" s="15" t="n"/>
-    </row>
-    <row r="8">
-      <c r="A8" s="20" t="n">
-        <v>3</v>
-      </c>
-      <c r="B8" s="9" t="inlineStr">
-        <is>
-          <t>Verificar estado: tornillos, estabilidad, pintura</t>
-        </is>
-      </c>
-      <c r="C8" s="10" t="inlineStr">
+      <c r="F9" s="30" t="n"/>
+      <c r="G9" s="30" t="n"/>
+    </row>
+    <row r="10">
+      <c r="A10" s="27" t="n">
+        <v>5</v>
+      </c>
+      <c r="B10" s="28" t="inlineStr">
+        <is>
+          <t>Colocar sombrillas/toldos y verificar mecanismo</t>
+        </is>
+      </c>
+      <c r="C10" s="29" t="inlineStr">
         <is>
           <t>Terraza</t>
         </is>
       </c>
-      <c r="D8" s="10" t="inlineStr">
+      <c r="D10" s="29" t="inlineStr">
+        <is>
+          <t>Auxiliar</t>
+        </is>
+      </c>
+      <c r="E10" s="29" t="inlineStr">
+        <is>
+          <t>Primavera</t>
+        </is>
+      </c>
+      <c r="F10" s="30" t="n"/>
+      <c r="G10" s="30" t="n"/>
+    </row>
+    <row r="11">
+      <c r="A11" s="31" t="n">
+        <v>6</v>
+      </c>
+      <c r="B11" s="32" t="inlineStr">
+        <is>
+          <t>Delimitar zona de terraza (vallas, maceteros)</t>
+        </is>
+      </c>
+      <c r="C11" s="29" t="inlineStr">
+        <is>
+          <t>Terraza</t>
+        </is>
+      </c>
+      <c r="D11" s="29" t="inlineStr">
         <is>
           <t>Manager</t>
         </is>
       </c>
-      <c r="E8" s="10" t="inlineStr">
+      <c r="E11" s="29" t="inlineStr">
         <is>
           <t>Primavera</t>
         </is>
       </c>
-      <c r="F8" s="11" t="n"/>
-      <c r="G8" s="11" t="n"/>
-    </row>
-    <row r="9">
-      <c r="A9" s="21" t="n">
-        <v>4</v>
-      </c>
-      <c r="B9" s="13" t="inlineStr">
-        <is>
-          <t>Colocar sombrillas/toldos y verificar mecanismo</t>
-        </is>
-      </c>
-      <c r="C9" s="14" t="inlineStr">
+      <c r="F11" s="30" t="n"/>
+      <c r="G11" s="30" t="n"/>
+    </row>
+    <row r="12">
+      <c r="A12" s="27" t="n">
+        <v>7</v>
+      </c>
+      <c r="B12" s="28" t="inlineStr">
+        <is>
+          <t>Colocar macetas, plantas y decoración</t>
+        </is>
+      </c>
+      <c r="C12" s="29" t="inlineStr">
         <is>
           <t>Terraza</t>
         </is>
       </c>
-      <c r="D9" s="14" t="inlineStr">
+      <c r="D12" s="29" t="inlineStr">
+        <is>
+          <t>Camarero/a</t>
+        </is>
+      </c>
+      <c r="E12" s="29" t="inlineStr">
+        <is>
+          <t>Primavera</t>
+        </is>
+      </c>
+      <c r="F12" s="30" t="n"/>
+      <c r="G12" s="30" t="n"/>
+    </row>
+    <row r="13">
+      <c r="A13" s="25" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  CIERRE DE TERRAZA (OTOÑO)</t>
+        </is>
+      </c>
+      <c r="B13" s="26" t="n"/>
+      <c r="C13" s="26" t="n"/>
+      <c r="D13" s="26" t="n"/>
+      <c r="E13" s="26" t="n"/>
+      <c r="F13" s="26" t="n"/>
+      <c r="G13" s="26" t="n"/>
+    </row>
+    <row r="14">
+      <c r="A14" s="27" t="n">
+        <v>8</v>
+      </c>
+      <c r="B14" s="28" t="inlineStr">
+        <is>
+          <t>Recoger decoración y plantas</t>
+        </is>
+      </c>
+      <c r="C14" s="29" t="inlineStr">
+        <is>
+          <t>Terraza</t>
+        </is>
+      </c>
+      <c r="D14" s="29" t="inlineStr">
+        <is>
+          <t>Camarero/a</t>
+        </is>
+      </c>
+      <c r="E14" s="29" t="inlineStr">
+        <is>
+          <t>Otoño</t>
+        </is>
+      </c>
+      <c r="F14" s="30" t="n"/>
+      <c r="G14" s="30" t="n"/>
+    </row>
+    <row r="15">
+      <c r="A15" s="31" t="n">
+        <v>9</v>
+      </c>
+      <c r="B15" s="32" t="inlineStr">
+        <is>
+          <t>Limpiar y secar todo el mobiliario</t>
+        </is>
+      </c>
+      <c r="C15" s="29" t="inlineStr">
+        <is>
+          <t>Terraza</t>
+        </is>
+      </c>
+      <c r="D15" s="29" t="inlineStr">
         <is>
           <t>Auxiliar</t>
         </is>
       </c>
-      <c r="E9" s="14" t="inlineStr">
-        <is>
-          <t>Primavera</t>
-        </is>
-      </c>
-      <c r="F9" s="15" t="n"/>
-      <c r="G9" s="15" t="n"/>
-    </row>
-    <row r="10">
-      <c r="A10" s="20" t="n">
-        <v>5</v>
-      </c>
-      <c r="B10" s="9" t="inlineStr">
-        <is>
-          <t>Colocar macetas, plantas y decoración</t>
-        </is>
-      </c>
-      <c r="C10" s="10" t="inlineStr">
-        <is>
-          <t>Terraza</t>
-        </is>
-      </c>
-      <c r="D10" s="10" t="inlineStr">
-        <is>
-          <t>Camarero/a</t>
-        </is>
-      </c>
-      <c r="E10" s="10" t="inlineStr">
-        <is>
-          <t>Primavera</t>
-        </is>
-      </c>
-      <c r="F10" s="11" t="n"/>
-      <c r="G10" s="11" t="n"/>
-    </row>
-    <row r="11">
-      <c r="A11" s="21" t="n">
-        <v>6</v>
-      </c>
-      <c r="B11" s="13" t="inlineStr">
-        <is>
-          <t>Delimitar zona de terraza (vallas, maceteros)</t>
-        </is>
-      </c>
-      <c r="C11" s="14" t="inlineStr">
-        <is>
-          <t>Terraza</t>
-        </is>
-      </c>
-      <c r="D11" s="14" t="inlineStr">
+      <c r="E15" s="29" t="inlineStr">
+        <is>
+          <t>Otoño</t>
+        </is>
+      </c>
+      <c r="F15" s="30" t="n"/>
+      <c r="G15" s="30" t="n"/>
+    </row>
+    <row r="16">
+      <c r="A16" s="27" t="n">
+        <v>10</v>
+      </c>
+      <c r="B16" s="28" t="inlineStr">
+        <is>
+          <t>Guardar sombrillas y toldos bien plegados</t>
+        </is>
+      </c>
+      <c r="C16" s="29" t="inlineStr">
+        <is>
+          <t>Almacén</t>
+        </is>
+      </c>
+      <c r="D16" s="29" t="inlineStr">
+        <is>
+          <t>Auxiliar</t>
+        </is>
+      </c>
+      <c r="E16" s="29" t="inlineStr">
+        <is>
+          <t>Otoño</t>
+        </is>
+      </c>
+      <c r="F16" s="30" t="n"/>
+      <c r="G16" s="30" t="n"/>
+    </row>
+    <row r="17">
+      <c r="A17" s="31" t="n">
+        <v>11</v>
+      </c>
+      <c r="B17" s="32" t="inlineStr">
+        <is>
+          <t>Guardar mobiliario en almacén (protegido)</t>
+        </is>
+      </c>
+      <c r="C17" s="29" t="inlineStr">
+        <is>
+          <t>Almacén</t>
+        </is>
+      </c>
+      <c r="D17" s="29" t="inlineStr">
+        <is>
+          <t>Auxiliar</t>
+        </is>
+      </c>
+      <c r="E17" s="29" t="inlineStr">
+        <is>
+          <t>Otoño</t>
+        </is>
+      </c>
+      <c r="F17" s="30" t="n"/>
+      <c r="G17" s="30" t="n"/>
+    </row>
+    <row r="18">
+      <c r="A18" s="27" t="n">
+        <v>12</v>
+      </c>
+      <c r="B18" s="28" t="inlineStr">
+        <is>
+          <t>Inventario de mobiliario: anotar roturas/reposiciones</t>
+        </is>
+      </c>
+      <c r="C18" s="29" t="inlineStr">
+        <is>
+          <t>Office</t>
+        </is>
+      </c>
+      <c r="D18" s="29" t="inlineStr">
         <is>
           <t>Manager</t>
         </is>
       </c>
-      <c r="E11" s="14" t="inlineStr">
-        <is>
-          <t>Primavera</t>
-        </is>
-      </c>
-      <c r="F11" s="15" t="n"/>
-      <c r="G11" s="15" t="n"/>
-    </row>
-    <row r="12">
-      <c r="A12" s="20" t="n">
-        <v>7</v>
-      </c>
-      <c r="B12" s="9" t="inlineStr">
-        <is>
-          <t>Verificar permiso de terraza vigente</t>
-        </is>
-      </c>
-      <c r="C12" s="10" t="inlineStr">
-        <is>
-          <t>Office</t>
-        </is>
-      </c>
-      <c r="D12" s="10" t="inlineStr">
-        <is>
-          <t>Manager</t>
-        </is>
-      </c>
-      <c r="E12" s="10" t="inlineStr">
-        <is>
-          <t>Primavera</t>
-        </is>
-      </c>
-      <c r="F12" s="11" t="n"/>
-      <c r="G12" s="11" t="n"/>
-    </row>
-    <row r="13">
-      <c r="A13" s="7" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  CIERRE DE TERRAZA (OTOÑO)</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" s="20" t="n">
-        <v>8</v>
-      </c>
-      <c r="B14" s="9" t="inlineStr">
-        <is>
-          <t>Recoger decoración y plantas</t>
-        </is>
-      </c>
-      <c r="C14" s="10" t="inlineStr">
-        <is>
-          <t>Terraza</t>
-        </is>
-      </c>
-      <c r="D14" s="10" t="inlineStr">
-        <is>
-          <t>Camarero/a</t>
-        </is>
-      </c>
-      <c r="E14" s="10" t="inlineStr">
+      <c r="E18" s="29" t="inlineStr">
         <is>
           <t>Otoño</t>
         </is>
       </c>
-      <c r="F14" s="11" t="n"/>
-      <c r="G14" s="11" t="n"/>
-    </row>
-    <row r="15">
-      <c r="A15" s="21" t="n">
-        <v>9</v>
-      </c>
-      <c r="B15" s="13" t="inlineStr">
-        <is>
-          <t>Limpiar y secar todo el mobiliario</t>
-        </is>
-      </c>
-      <c r="C15" s="14" t="inlineStr">
-        <is>
-          <t>Terraza</t>
-        </is>
-      </c>
-      <c r="D15" s="14" t="inlineStr">
-        <is>
-          <t>Auxiliar</t>
-        </is>
-      </c>
-      <c r="E15" s="14" t="inlineStr">
-        <is>
-          <t>Otoño</t>
-        </is>
-      </c>
-      <c r="F15" s="15" t="n"/>
-      <c r="G15" s="15" t="n"/>
-    </row>
-    <row r="16">
-      <c r="A16" s="20" t="n">
-        <v>10</v>
-      </c>
-      <c r="B16" s="9" t="inlineStr">
-        <is>
-          <t>Guardar sombrillas y toldos bien plegados</t>
-        </is>
-      </c>
-      <c r="C16" s="10" t="inlineStr">
-        <is>
-          <t>Almacén</t>
-        </is>
-      </c>
-      <c r="D16" s="10" t="inlineStr">
-        <is>
-          <t>Auxiliar</t>
-        </is>
-      </c>
-      <c r="E16" s="10" t="inlineStr">
-        <is>
-          <t>Otoño</t>
-        </is>
-      </c>
-      <c r="F16" s="11" t="n"/>
-      <c r="G16" s="11" t="n"/>
-    </row>
-    <row r="17">
-      <c r="A17" s="21" t="n">
-        <v>11</v>
-      </c>
-      <c r="B17" s="13" t="inlineStr">
-        <is>
-          <t>Guardar mobiliario en almacén (protegido)</t>
-        </is>
-      </c>
-      <c r="C17" s="14" t="inlineStr">
-        <is>
-          <t>Almacén</t>
-        </is>
-      </c>
-      <c r="D17" s="14" t="inlineStr">
-        <is>
-          <t>Auxiliar</t>
-        </is>
-      </c>
-      <c r="E17" s="14" t="inlineStr">
-        <is>
-          <t>Otoño</t>
-        </is>
-      </c>
-      <c r="F17" s="15" t="n"/>
-      <c r="G17" s="15" t="n"/>
-    </row>
-    <row r="18">
-      <c r="A18" s="20" t="n">
-        <v>12</v>
-      </c>
-      <c r="B18" s="9" t="inlineStr">
-        <is>
-          <t>Inventario de mobiliario: anotar roturas/reposiciones</t>
-        </is>
-      </c>
-      <c r="C18" s="10" t="inlineStr">
-        <is>
-          <t>Office</t>
-        </is>
-      </c>
-      <c r="D18" s="10" t="inlineStr">
-        <is>
-          <t>Manager</t>
-        </is>
-      </c>
-      <c r="E18" s="10" t="inlineStr">
-        <is>
-          <t>Otoño</t>
-        </is>
-      </c>
-      <c r="F18" s="11" t="n"/>
-      <c r="G18" s="11" t="n"/>
-    </row>
-    <row r="19"/>
+      <c r="F18" s="30" t="n"/>
+      <c r="G18" s="30" t="n"/>
+    </row>
+    <row r="19">
+      <c r="A19" s="33" t="n"/>
+      <c r="B19" s="34" t="n"/>
+      <c r="C19" s="29" t="n"/>
+      <c r="D19" s="29" t="n"/>
+      <c r="E19" s="29" t="n"/>
+      <c r="F19" s="30" t="n"/>
+      <c r="G19" s="30" t="n"/>
+    </row>
     <row r="20">
-      <c r="C20" s="16" t="inlineStr">
-        <is>
-          <t>Completadas:</t>
-        </is>
-      </c>
-      <c r="D20" s="17">
-        <f>COUNTIF(F5:F18,"✓")</f>
+      <c r="A20" s="33" t="n"/>
+      <c r="B20" s="34" t="n"/>
+      <c r="C20" s="29" t="n"/>
+      <c r="D20" s="29" t="n"/>
+      <c r="E20" s="29" t="n"/>
+      <c r="F20" s="30" t="n"/>
+      <c r="G20" s="30" t="n"/>
+    </row>
+    <row r="21">
+      <c r="A21" s="33" t="n"/>
+      <c r="B21" s="34" t="n"/>
+      <c r="C21" s="29" t="n"/>
+      <c r="D21" s="29" t="n"/>
+      <c r="E21" s="29" t="n"/>
+      <c r="F21" s="30" t="n"/>
+      <c r="G21" s="30" t="n"/>
+    </row>
+    <row r="22">
+      <c r="A22" s="33" t="n"/>
+      <c r="B22" s="34" t="n"/>
+      <c r="C22" s="29" t="n"/>
+      <c r="D22" s="29" t="n"/>
+      <c r="E22" s="29" t="n"/>
+      <c r="F22" s="30" t="n"/>
+      <c r="G22" s="30" t="n"/>
+    </row>
+    <row r="23">
+      <c r="A23" s="33" t="n"/>
+      <c r="B23" s="34" t="n"/>
+      <c r="C23" s="29" t="n"/>
+      <c r="D23" s="29" t="n"/>
+      <c r="E23" s="29" t="n"/>
+      <c r="F23" s="30" t="n"/>
+      <c r="G23" s="30" t="n"/>
+    </row>
+    <row r="24"/>
+    <row r="25">
+      <c r="A25" s="16" t="inlineStr">
+        <is>
+          <t>Tareas completadas:</t>
+        </is>
+      </c>
+      <c r="D25" s="17">
+        <f>COUNTIFS(B5:B23,"?*",F5:F23,"✓")</f>
         <v>0.0</v>
       </c>
-      <c r="E20" s="16" t="inlineStr">
+      <c r="E25" s="16" t="inlineStr">
         <is>
           <t>de</t>
         </is>
       </c>
-      <c r="F20">
-        <f>COUNTIF(B5:B18,"?*")</f>
+      <c r="F25">
+        <f>COUNTIF(B5:B23,"?*")-COUNTIF(F5:F23,"N/A")</f>
         <v>12.0</v>
       </c>
     </row>
-    <row r="21"/>
-    <row r="22">
-      <c r="A22" s="18" t="inlineStr">
+    <row r="26"/>
+    <row r="27">
+      <c r="A27" s="18" t="inlineStr">
         <is>
           <t>Firma encargado/a: _________________________    Hora: _________</t>
         </is>
       </c>
     </row>
-    <row r="23"/>
-    <row r="24">
-      <c r="A24" s="19" t="inlineStr">
-        <is>
-          <t>— Kit de Tareas Recurrentes: Cafetería / Brunch · AI Chef Pro · aichef.pro —</t>
+    <row r="28"/>
+    <row r="29">
+      <c r="A29" s="19" t="inlineStr">
+        <is>
+          <t>— Kit de Tareas Recurrentes · Cafetería / Brunch · AI Chef Pro · aichef.pro</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="6">
+  <sheetProtection selectLockedCells="0" selectUnlockedCells="0" sheet="1" objects="0" insertRows="0" insertHyperlinks="1" autoFilter="0" scenarios="0" formatColumns="0" deleteColumns="1" insertColumns="1" pivotTables="1" deleteRows="0" formatCells="0" formatRows="0" sort="0"/>
+  <mergeCells count="7">
     <mergeCell ref="A1:G1"/>
+    <mergeCell ref="A27:G27"/>
     <mergeCell ref="A13:G13"/>
     <mergeCell ref="A2:G2"/>
-    <mergeCell ref="A24:G24"/>
+    <mergeCell ref="A25:C25"/>
     <mergeCell ref="A5:G5"/>
-    <mergeCell ref="A22:G22"/>
+    <mergeCell ref="A29:G29"/>
   </mergeCells>
-  <conditionalFormatting sqref="A5:G18">
+  <conditionalFormatting sqref="A5:G23">
     <cfRule type="expression" priority="1" dxfId="0">
       <formula>$F5="✓"</formula>
     </cfRule>
   </conditionalFormatting>
   <dataValidations count="1">
-    <dataValidation sqref="F6 F7 F8 F9 F10 F11 F12 F14 F15 F16 F17 F18" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="F6 F7 F8 F9 F10 F11 F12 F14 F15 F16 F17 F18 F19 F20 F21 F22 F23" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Marca no válida" error="Usa el desplegable: ✓, — o N/A. N/A = no aplica, sale del total; — = no hecha, cuenta como pendiente." type="list" errorStyle="stop">
       <formula1>"✓,—,N/A"</formula1>
     </dataValidation>
   </dataValidations>
